--- a/output/google_jobs.xlsx
+++ b/output/google_jobs.xlsx
@@ -425,12 +425,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R22"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
@@ -579,7 +579,7 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>5 days ago</t>
+          <t>6 days ago</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -717,17 +717,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NIEPID Special Educator Recruitment 2026 | TrueJobs</t>
+          <t>Jr.Community Coordinator (Jr.Early Interventionist)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>National Institute for the Empowerment of Persons with Intellectual Disabilities (DIVYANGJAN)</t>
+          <t>The Association of People with disability</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Secunderabad, Telangana</t>
+          <t>Hoskote, Karnataka</t>
         </is>
       </c>
       <c r="D5" t="b">
@@ -754,7 +754,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>https://truejobs.co.in/jobs/employment-news/niepid-special-educator-recruitment-2026-secunderabad?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+          <t>https://bebee.com/in/jobs/jrcommunity-coordinator-jrearly-interventionist-the-association-of-people-with-disability-hosakote-k--theirstack-660265567?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -764,24 +764,24 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>About the OrganisationThe National Institute for the Empowerment of Persons with Intellectual Disabilities (NIEPID), formerly known as NIMH, is an autonomous body under the Department of Empowerment of Persons with Disabilities (Divyangjan), Ministry of Social Justice &amp; Empowerment, Government of In</t>
+          <t>### Job Information Industry NGO Salary 2.40 LPA - 3.5 LPA Date Opened 04/03/2026 Job Type Full time Work Experience 0-1 year City Hosakote State/Province Karnataka Country India Zip/Postal Code 562114 ### About Us Valid ### Job Description Job Title: Jr. Early Interventionist Department: Early Inte</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Purchase Executive (People with Disability only)</t>
+          <t>Billing - Executive - Only person with disability</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kanz</t>
+          <t>Jobs for Humanity</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Hosur, Tamil Nadu</t>
         </is>
       </c>
       <c r="D6" t="b">
@@ -789,7 +789,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>internship</t>
+          <t>job</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -808,7 +808,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/purchase-executive-people-with-disability-only-at-kanz-4334091883?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+          <t>https://jobs.smartrecruiters.com/JobsForHumanity/744000009789585-billing-executive-only-person-with-disability?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -818,24 +818,24 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Greetings from Saira Jobs! We are currently recruiting for a 'Purchase Executive (Packing Materials)' on behalf of our partner. Explore the opportunity below and apply today if you meet the qualifications! Job Purpose : Effectively raising of purchase orders and ensure 100% servicing to avoid any pr</t>
+          <t>Company DescriptionSaira's clientJob DescriptionOpen Requirements for Person with DisabilityRole- Billing ExecutiveWork Mode- Work from OfficeInterview Mode- Walk in InterviewLocation- HosurExperience- 3-5 YearsCtc- 4-6LPADisability Type- Locomotor Disability, Low Vision, Hard of Hearing, Dwarfism,</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jr.Community Coordinator (Jr.Early Interventionist)</t>
+          <t>Financial Analyst- Only PERSON WITH DISABILITY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Association of People with disability</t>
+          <t>Kanz</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hoskote, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D7" t="b">
@@ -862,7 +862,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>https://bebee.com/in/jobs/jrcommunity-coordinator-jrearly-interventionist-the-association-of-people-with-disability-hosakote-k--theirstack-660265567?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+          <t>https://in.linkedin.com/jobs/view/financial-analyst-only-person-with-disability-at-kanz-4333588376?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -872,24 +872,24 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>### Job Information Industry NGO Salary 2.40 LPA - 3.5 LPA Date Opened 04/03/2026 Job Type Full time Work Experience 0-1 year City Hosakote State/Province Karnataka Country India Zip/Postal Code 562114 ### About Us Valid ### Job Description Job Title: Jr. Early Interventionist Department: Early Inte</t>
+          <t>Saira's client Analyst Roles &amp; Responsibilities  Working on back office and middle office processes for financial institutions  Handling different stages of client/product life cycle across stages - KYC, reference data management, legal docs, loans, portfolio reconciliation, document capture, syst</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Billing - Executive - Only person with disability</t>
+          <t>India Work Placement Coordinator</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jobs for Humanity</t>
+          <t>Disability Rights Promotion International</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hosur, Tamil Nadu</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="D8" t="b">
@@ -897,7 +897,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>internship</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -916,7 +916,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/JobsForHumanity/744000009789585-billing-executive-only-person-with-disability?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+          <t>https://a11y.enabled.in/dpri-hiring-india-work-placement-coordinator/?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -926,19 +926,19 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Company DescriptionSaira's clientJob DescriptionOpen Requirements for Person with DisabilityRole- Billing ExecutiveWork Mode- Work from OfficeInterview Mode- Walk in InterviewLocation- HosurExperience- 3-5 YearsCtc- 4-6LPADisability Type- Locomotor Disability, Low Vision, Hard of Hearing, Dwarfism,</t>
+          <t>Description: Disability Rights Promotion International</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Financial Analyst- Only PERSON WITH DISABILITY</t>
+          <t>DEI / LGBTQIA + Person with disability - Public Relations Intern</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kanz</t>
+          <t>Burson</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>internship</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -967,10 +967,14 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>7 days ago</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/financial-analyst-only-person-with-disability-at-kanz-4333588376?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+          <t>https://www.glassdoor.co.in/job-listing/dei-lgbtqia-person-with-disability-public-relations-intern-burson-JV_KO0,58_KE59,65.htm?jl=1009974840240&amp;utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -980,24 +984,24 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Saira's client Analyst Roles &amp; Responsibilities  Working on back office and middle office processes for financial institutions  Handling different stages of client/product life cycle across stages - KYC, reference data management, legal docs, loans, portfolio reconciliation, document capture, syst</t>
+          <t>Who we are: Burson, part of WPP, is the global communications leader built to create value for clients through reputation. With highly specialized teams, industry-leading technologies and breakthrough creative, we help brands and businesses redefine reputation as a competitive advantage so they can</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>India Work Placement Coordinator</t>
+          <t>Sales Manager Kolkata (India)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Disability Rights Promotion International</t>
+          <t>Divyang Bhartia</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Kolkata, West Bengal</t>
         </is>
       </c>
       <c r="D10" t="b">
@@ -1005,7 +1009,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>internship</t>
+          <t>job</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1021,10 +1025,14 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>4 days ago</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>https://a11y.enabled.in/dpri-hiring-india-work-placement-coordinator/?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+          <t>https://in.jobrapido.com/jobpreview/7666997820758425600?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1034,19 +1042,19 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Description: Disability Rights Promotion International</t>
+          <t>Responsibilities Manage key partnerships, drive revenue growth. Lead strategic planning, oversee sales strategy. Drive channel sales through CRM &amp; consulting. Build robust relationships with clients &amp; partners. Perks and advantages Health insurance</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DEI / LGBTQIA + Person with disability - Public Relations Intern</t>
+          <t>Trained Caregiver/ Divyang Mitra</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Burson</t>
+          <t>Composite Regional Centre for Skill Development Rehabilitation &amp; Empowerment of Persons with Disabilities (CRC-Bhopal)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1059,7 +1067,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>internship</t>
+          <t>job</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1077,12 +1085,12 @@
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>6 days ago</t>
+          <t>3 days ago</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.co.in/job-listing/dei-lgbtqia-person-with-disability-public-relations-intern-burson-JV_KO0,58_KE59,65.htm?jl=1009974840240&amp;utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+          <t>https://www.aspirantai.co.in/trained-caregiver-divyang-mitra--crc-bhopal-recruitment-2026-apply-offline-for-10-nurse-physiotherapist-and-more-posts-3044069--88c76bb169a8?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1092,24 +1100,24 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Who we are: Burson, part of WPP, is the global communications leader built to create value for clients through reputation. With highly specialized teams, industry-leading technologies and breakthrough creative, we help brands and businesses redefine reputation as a competitive advantage so they can</t>
+          <t>Qualification: MPhil, PGDRP, PDCP, Bachelor in Occupational Therapy, B.Sc, Degree in Speech and Language Sciences, BASLP, DECSE, D.Ed., B.Ed., Bachelor in Physiotherapy, Diploma or BSc Nursing, RCI/National Trust certified Course in Caregiving OR 3-year experience in caregiving of CWSN. Clinical / R</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sales Manager Kolkata (India)</t>
+          <t>Oil India Limited PwBD Recruitment 2026 – Apply for 49 Posts</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Divyang Bhartia</t>
+          <t>Oil India Limited (OIL), Ministry of Petroleum and Natural Gas, Government of India</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kolkata, West Bengal</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="D12" t="b">
@@ -1127,20 +1135,28 @@
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>₹26.6K–₹1.45L a month</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>319200</v>
+      </c>
+      <c r="M12" t="n">
+        <v>17400</v>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>3 days ago</t>
+          <t>18 days ago</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>https://in.jobrapido.com/jobpreview/7666997820758425600?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+          <t>https://jobone.in/job/oil-india-limited-oil-india-limited-pwbd-2026-for-49-recruitment-2026?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1150,28 +1166,28 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Responsibilities Manage key partnerships, drive revenue growth. Lead strategic planning, oversee sales strategy. Drive channel sales through CRM &amp; consulting. Build robust relationships with clients &amp; partners. Perks and advantages Health insurance</t>
+          <t>Quick Info Overview OrganizationOil India Limited (OIL), Ministry of Petroleum and Natural Gas, Government of India Post NameOil India Limited PwBD Recruitment 2026 – Apply for 49 Posts Total Vacancies49 CategoryCentral Govt Jobs LocationAssam Education10th_pass, 12th_pass, diploma Age Limit40 Yrs (</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Educational Video Editor</t>
+          <t>Oil India PwBD Workperson Recruitment 2026: 49 Workperson Posts</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Divyang</t>
+          <t>Oil India Limited</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Anywhere</t>
+          <t>Duliajan, Assam</t>
         </is>
       </c>
       <c r="D13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1187,26 +1203,26 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>₹5K–₹15K a month</t>
+          <t>₹26.6K–₹1.45L a month</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>60000</v>
+        <v>319200</v>
       </c>
       <c r="M13" t="n">
-        <v>180000</v>
+        <v>17400</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t>9 days ago</t>
+          <t>18 days ago</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>https://www.rockerstop.com/jobs/Educational-Video-Editor/9412?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+          <t>https://www.sarkarirojgarkendra.com/oil-india-pwbd-workperson-may-2026/?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1216,32 +1232,32 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Hello. I want someone to edit my videos of Live Classes i conduct Online through OBS . I take Math Classes from Grade 8-12 which are generally consist of 40 min each which i want to cut it to 20-25 min. There are such 3-4 classes daily ,so its a long term project . I have shared one sample video htt</t>
+          <t>Oil India Limited invites online applications for 49 PwBD Workperson posts including Junior Technician, Junior Office Assistant, and Junior Engineer vacancies. Eligible candidates from Assam and Arunachal Pradesh can apply online before 08 June 2026.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Trained Caregiver/ Divyang Mitra</t>
+          <t>Compassionate Remote Crisis Chat &amp; Text Counselor – Full‑Time Position with arenaflex Supporting Deaf, Hard‑of‑Hearing &amp; Deaf‑Plus Communities</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Composite Regional Centre for Skill Development Rehabilitation &amp; Empowerment of Persons with Disabilities (CRC-Bhopal)</t>
+          <t>remotepromsp</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Anywhere</t>
         </is>
       </c>
       <c r="D14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>internship</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1259,12 +1275,12 @@
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2 days ago</t>
+          <t>5 days ago</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>https://www.aspirantai.co.in/trained-caregiver-divyang-mitra--crc-bhopal-recruitment-2026-apply-offline-for-10-nurse-physiotherapist-and-more-posts-3044069--88c76bb169a8?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+          <t>https://www.mysmartpros.com/remotepro/job/1704329?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1274,32 +1290,32 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Qualification: MPhil, PGDRP, PDCP, Bachelor in Occupational Therapy, B.Sc, Degree in Speech and Language Sciences, BASLP, DECSE, D.Ed., B.Ed., Bachelor in Physiotherapy, Diploma or BSc Nursing, RCI/National Trust certified Course in Caregiving OR 3-year experience in caregiving of CWSN. Clinical / R</t>
+          <t>```html About arenaflex – A Mission‑Driven Non‑Profit Championing Crisis Support At arenaflex, we are dedicated to safeguarding the emotional and physical well‑being of individuals who are Deaf, Hard of Hearing, Late‑Deafened, DeafBlind, DeafDisabled, and Deaf+. Operating across Missouri and extendi</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Oil India Limited PwBD Recruitment 2026 – Apply for 49 Posts</t>
+          <t>Urgently Require Special Education Teacher Deaf &amp; Hard of Hearing DHH (ID 2417) in San Diego, CA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Oil India Limited (OIL), Ministry of Petroleum and Natural Gas, Government of India</t>
+          <t>remotepromsp</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Anywhere</t>
         </is>
       </c>
       <c r="D15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>internship</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1309,28 +1325,20 @@
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>₹26.6K–₹1.45L a month</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="n">
-        <v>319200</v>
-      </c>
-      <c r="M15" t="n">
-        <v>17400</v>
-      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>17 days ago</t>
+          <t>7 days ago</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>https://jobone.in/job/oil-india-limited-oil-india-limited-pwbd-2026-for-49-recruitment-2026?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+          <t>https://www.mysmartpros.com/remotepro/job/199232?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1340,28 +1348,28 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Quick Info Overview OrganizationOil India Limited (OIL), Ministry of Petroleum and Natural Gas, Government of India Post NameOil India Limited PwBD Recruitment 2026 – Apply for 49 Posts Total Vacancies49 CategoryCentral Govt Jobs LocationAssam Education10th_pass, 12th_pass, diploma Age Limit40 Yrs (</t>
+          <t>Job title: Special Education Teacher Deaf &amp; Hard of Hearing DHH (ID 2417) Company: San Diego County Office of Education Job description: Job Summary Join our amazing team The San Diego County Office of Education is a collaborative organization that works toward a future without boundaries for our st</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Oil India PwBD Workperson Recruitment 2026: 49 Workperson Posts</t>
+          <t>Remote Teacher for Deaf / Hard of Hearing in Schools | WFH</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Oil India Limited</t>
+          <t>remotepromsp</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Duliajan, Assam</t>
+          <t>Anywhere</t>
         </is>
       </c>
       <c r="D16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1375,28 +1383,20 @@
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>₹26.6K–₹1.45L a month</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="n">
-        <v>319200</v>
-      </c>
-      <c r="M16" t="n">
-        <v>17400</v>
-      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>17 days ago</t>
+          <t>5 days ago</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>https://www.sarkarirojgarkendra.com/oil-india-pwbd-workperson-may-2026/?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+          <t>https://www.mysmartpros.com/remotepro/job/442673?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Oil India Limited invites online applications for 49 PwBD Workperson posts including Junior Technician, Junior Office Assistant, and Junior Engineer vacancies. Eligible candidates from Assam and Arunachal Pradesh can apply online before 08 June 2026.</t>
+          <t>Job Overview We are dedicated to delivering exceptional, inclusive education that empowers all students, recognizing the value of diverse learning experiences. Our mission is to cultivate an environment where students who are Deaf and Hard of Hearing can flourish. We invite passionate and qualified</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Compassionate Remote Crisis Chat &amp; Text Counselor – Full‑Time Position with arenaflex Supporting Deaf, Hard‑of‑Hearing &amp; Deaf‑Plus Communities</t>
+          <t>Immediately Need NON-CLASSIFIED: Teacher of the Deaf: Elementary in Colorado Springs, CO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1449,12 +1449,12 @@
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>4 days ago</t>
+          <t>8 days ago</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>https://www.mysmartpros.com/remotepro/job/1704329?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+          <t>https://www.mysmartpros.com/remotepro/job/196421?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1464,14 +1464,14 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>```html About arenaflex – A Mission‑Driven Non‑Profit Championing Crisis Support At arenaflex, we are dedicated to safeguarding the emotional and physical well‑being of individuals who are Deaf, Hard of Hearing, Late‑Deafened, DeafBlind, DeafDisabled, and Deaf+. Operating across Missouri and extendi</t>
+          <t>Job title: NON-CLASSIFIED: Teacher of the Deaf: Elementary Company: State of Colorado Job description: Department Information Vision Statement: CSDB aspires to be an exemplary global resource for families and professionals that excels in preparing diverse learners to transform the world with PRIDE:</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Urgently Require Special Education Teacher Deaf &amp; Hard of Hearing DHH (ID 2417) in San Diego, CA</t>
+          <t>[Remote-Position] Looking for WLMS ParaEducator, Deaf /Hard of</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>internship</t>
+          <t>job</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1507,12 +1507,12 @@
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>6 days ago</t>
+          <t>8 days ago</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>https://www.mysmartpros.com/remotepro/job/199232?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+          <t>https://www.mysmartpros.com/remotepro/job/829755?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -1522,239 +1522,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Job title: Special Education Teacher Deaf &amp; Hard of Hearing DHH (ID 2417) Company: San Diego County Office of Education Job description: Job Summary Join our amazing team The San Diego County Office of Education is a collaborative organization that works toward a future without boundaries for our st</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Remote Teacher for Deaf / Hard of Hearing in Schools | WFH</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>remotepromsp</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Anywhere</t>
-        </is>
-      </c>
-      <c r="D19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>job</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>keyword_pwd</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>4 days ago</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>https://www.mysmartpros.com/remotepro/job/442673?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>google_jobs</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>Job Overview We are dedicated to delivering exceptional, inclusive education that empowers all students, recognizing the value of diverse learning experiences. Our mission is to cultivate an environment where students who are Deaf and Hard of Hearing can flourish. We invite passionate and qualified</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Immediately Need NON-CLASSIFIED: Teacher of the Deaf: Elementary in Colorado Springs, CO</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>remotepromsp</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Anywhere</t>
-        </is>
-      </c>
-      <c r="D20" t="b">
-        <v>1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>internship</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>keyword_pwd</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>7 days ago</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>https://www.mysmartpros.com/remotepro/job/196421?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>google_jobs</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>Job title: NON-CLASSIFIED: Teacher of the Deaf: Elementary Company: State of Colorado Job description: Department Information Vision Statement: CSDB aspires to be an exemplary global resource for families and professionals that excels in preparing diverse learners to transform the world with PRIDE:</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>[Remote-Position] Looking for WLMS ParaEducator, Deaf /Hard of</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>remotepromsp</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Anywhere</t>
-        </is>
-      </c>
-      <c r="D21" t="b">
-        <v>1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>job</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>keyword_pwd</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>7 days ago</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>https://www.mysmartpros.com/remotepro/job/829755?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>google_jobs</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
           <t>Quick Overview:Position: Looking For WLMS Paraeducator, Deaf /hard Of HearingCompany: Thornton, COLocation: RemoteStart Date: Immediate openings availableCompensation: a competitive salaryÂ Â Job title: WLMS ParaEducator, Deaf /Hard of Hearing Company: Adams County School District 12 Job description</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Speech Language Pathologist - School for disabled (Sultan Bathery)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Nameless</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="D22" t="b">
-        <v>0</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>job</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>keyword_pwd</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2 days ago</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>https://in.jobrapido.com/jobpreview/1542991832441421824?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>google_jobs</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>- Assessment and Diagnosis:&lt;\/b&gt; &lt;\/span&gt;Evaluate patients to identify speech, language, cognitive -communication, and swallowing disorders. &lt;\/li&gt; - Treatment Planning and Implementation:&lt;\/b&gt; &lt;\/span&gt;Develop and execute individualized therapy plans to address specific functional needs. &lt;\/li&gt; - Pa</t>
         </is>
       </c>
     </row>

--- a/output/google_jobs.xlsx
+++ b/output/google_jobs.xlsx
@@ -425,24 +425,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:R111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="47" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="29" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="13" customWidth="1" min="17" max="17"/>
     <col width="60" customWidth="1" min="18" max="18"/>
@@ -543,12 +543,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Manager Programs – Persons with Disability</t>
+          <t>Youth Prevention Specialist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Azim Premji Foundation</t>
+          <t>Gang Alternative, Inc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -571,20 +571,28 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>$40k - $45k</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>40000</v>
+      </c>
+      <c r="M2" t="n">
+        <v>40000</v>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>6 days ago</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/manager-programs-%E2%80%93-persons-with-disability-at-azim-premji-foundation-4416113352?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+          <t>https://jooble.org/jdp/-674747735150121535?ckey=PWD+disability+deaf+hearing+impaired+jobs&amp;rgn=55126&amp;pos=1&amp;groupId=40165&amp;elckey=7700453530903112052&amp;p=1&amp;aq=-4535327467038468568&amp;cid=12571&amp;jobAge=263&amp;brelb=100&amp;bscr=6.844701&amp;scr=6.844701</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -594,24 +602,24 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>About the role Under this theme, we support organisations that address the diverse needs of Persons with Disabilities in urban, rural and tribal areas across India.Our areas of engagement include early intervention, special and inclusive education, vocational and livelihood opportunities, recreation</t>
+          <t>&amp;nbsp;...position requires the ability to walk, sit, stand, reach, talk, &lt;b&gt;hear &lt;/b&gt;and lift presentation materials, including equipment....&amp;nbsp;&amp;nbsp;...without regard to race, color, religion, sex, national origin, &lt;b&gt;disability,&lt;/b&gt; marital status, or sexual orientation, in accordance with fede</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Director of Health &amp; Rehabilitation</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Association Of People With Disability</t>
+          <t>Blocky Smarty Blockchain Private Limited</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bengaluru, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D3" t="b">
@@ -629,24 +637,20 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>₹1,00,000–₹1,33,333 a month</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1599996</v>
-      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>https://bebee.com/in/jobs/director-of-health-rehabilitation-the-association-of-people-with-disability-bengaluru--theirstack-654777178?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+          <t>https://jooble.org/desc/-5374298963695325744?ckey=PWD+disability+deaf+hearing+impaired+jobs&amp;rgn=55126&amp;pos=2&amp;groupId=40165&amp;elckey=7700453530903112052&amp;p=1&amp;aq=-4535327467038468568&amp;cid=12571&amp;jobAge=2094&amp;brelb=100&amp;bscr=5.9563065&amp;scr=5.9563065</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -656,24 +660,24 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Director–Health &amp; Rehabilitation leads APD’s Early Intervention &amp; SCIR programs—driving strategy, multi-state operations, innovation, partnerships, research, and funding; ensures quality, scalability, team leadership, and measurable impact.</t>
+          <t>Dear All,We are Looking for a Director ( Person with &lt;b&gt;Disability)&lt;/b&gt; for our Company.Blocky Smarty Blockchain Private Limited.Qualifications:Experience inLeadership.Teamwork.Marketing and Sales.Finance and Accounting.Law.HR.Administration.Roles and Responsibilities.Independent...&amp;nbsp;</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Business Analyst- only person with disability</t>
+          <t>Quality Analyst, Trust &amp; Safety Ops (Bangalore)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jobs for Humanity</t>
+          <t>Moonpay</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D4" t="b">
@@ -697,10 +701,14 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/JobsForHumanity/744000017174060-business-analyst-only-person-with-disability?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+          <t>https://jooble.org/desc/7558807824368653182?ckey=PWD+disability+deaf+hearing+impaired+jobs&amp;rgn=55126&amp;pos=3&amp;groupId=40165&amp;elckey=7700453530903112052&amp;p=1&amp;aq=-4535327467038468568&amp;cid=12571&amp;jobAge=942&amp;brelb=100&amp;bscr=5.581216&amp;scr=5.581216</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -710,24 +718,24 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Company DescriptionSaira's clientJob DescriptionRole: Business AnalystLocation: HyderabadWork mode: Work from officePWD Category: Locomotor DisabilityMandatory skill: Experience with SQL or ETLKey Skill Set: SQL expertise or ETL, dashboard building experience. 2+ years of Excel or Tableau (data mani</t>
+          <t>&amp;nbsp;...indicative, and that we would still love to &lt;b&gt;hear &lt;/b&gt;from you even if you feel that you are...&amp;nbsp;&amp;nbsp;..., gender identity, national origin, age, &lt;b&gt;disability,&lt;/b&gt; protected veteran status or any other characteristic...&amp;nbsp;&amp;nbsp;...reasonable accommodations in our &lt;b&gt;job &lt;/b&gt;appli</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jr.Community Coordinator (Jr.Early Interventionist)</t>
+          <t>KYB Operations Analyst</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Association of People with disability</t>
+          <t>Moonpay</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Hoskote, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D5" t="b">
@@ -751,10 +759,14 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>https://bebee.com/in/jobs/jrcommunity-coordinator-jrearly-interventionist-the-association-of-people-with-disability-hosakote-k--theirstack-660265567?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+          <t>https://jooble.org/desc/-5210332800839519353?ckey=PWD+disability+deaf+hearing+impaired+jobs&amp;rgn=55126&amp;pos=4&amp;groupId=40165&amp;elckey=7700453530903112052&amp;p=1&amp;aq=-4535327467038468568&amp;cid=12571&amp;jobAge=30&amp;brelb=100&amp;bscr=5.251972&amp;scr=5.251972</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -764,24 +776,24 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>### Job Information Industry NGO Salary 2.40 LPA - 3.5 LPA Date Opened 04/03/2026 Job Type Full time Work Experience 0-1 year City Hosakote State/Province Karnataka Country India Zip/Postal Code 562114 ### About Us Valid ### Job Description Job Title: Jr. Early Interventionist Department: Early Inte</t>
+          <t>&amp;nbsp;...indicative, and that we would still love to &lt;b&gt;hear &lt;/b&gt;from you even if you feel that you are...&amp;nbsp;&amp;nbsp;..., gender identity, national origin, age, &lt;b&gt;disability,&lt;/b&gt; protected veteran status or any other characteristic...&amp;nbsp;&amp;nbsp;...reasonable accommodations in our &lt;b&gt;job &lt;/b&gt;appli</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Billing - Executive - Only person with disability</t>
+          <t>Client Account Director - NatSec/Intelligence</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jobs for Humanity</t>
+          <t>Chainalysis</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hosur, Tamil Nadu</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D6" t="b">
@@ -805,10 +817,14 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/JobsForHumanity/744000009789585-billing-executive-only-person-with-disability?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+          <t>https://jooble.org/desc/-461712511718551190?ckey=PWD+disability+deaf+hearing+impaired+jobs&amp;rgn=55126&amp;pos=5&amp;groupId=40165&amp;elckey=7700453530903112052&amp;p=1&amp;aq=-4535327467038468568&amp;cid=12571&amp;jobAge=1158&amp;brelb=100&amp;bscr=4.2491565&amp;scr=4.2491565</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -818,19 +834,19 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Company DescriptionSaira's clientJob DescriptionOpen Requirements for Person with DisabilityRole- Billing ExecutiveWork Mode- Work from OfficeInterview Mode- Walk in InterviewLocation- HosurExperience- 3-5 YearsCtc- 4-6LPADisability Type- Locomotor Disability, Low Vision, Hard of Hearing, Dwarfism,</t>
+          <t>&amp;nbsp;..., gender/gender expression, age, spirituality, ability, experience and more. If you need any accommodations to make our interview process more accessible to you due to a &lt;b&gt;disability,&lt;/b&gt; don't hesitate to let us know. You can learn more [here]( We can’t wait to meet you....&amp;nbsp;</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Financial Analyst- Only PERSON WITH DISABILITY</t>
+          <t>Application Development Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kanz</t>
+          <t>Momentive</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -859,10 +875,14 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>https://in.linkedin.com/jobs/view/financial-analyst-only-person-with-disability-at-kanz-4333588376?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+          <t>https://jooble.org/desc/-2396562862812582815?ckey=PWD+disability+deaf+hearing+impaired+jobs&amp;rgn=55126&amp;pos=6&amp;groupId=40165&amp;elckey=7700453530903112052&amp;p=1&amp;aq=-4535327467038468568&amp;cid=12571&amp;jobAge=7158&amp;brelb=100&amp;bscr=4.063623&amp;scr=4.063623</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -872,24 +892,24 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Saira's client Analyst Roles &amp; Responsibilities  Working on back office and middle office processes for financial institutions  Handling different stages of client/product life cycle across stages - KYC, reference data management, legal docs, loans, portfolio reconciliation, document capture, syst</t>
+          <t>&amp;nbsp;...&lt;b&gt;Job &lt;/b&gt;Title: Application Development Engineer Summary: The position is focused on products in the Polyurethane Slab Stock...&amp;nbsp;&amp;nbsp;...religion, sex, sexual orientation, gender identity, national origin, &lt;b&gt;disability,&lt;/b&gt; status as a protected veteran, or any characteristic protec</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>India Work Placement Coordinator</t>
+          <t>Manual Quality Assurance Engineer, SIMBA Team - Noida, India</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Disability Rights Promotion International</t>
+          <t>speechify</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D8" t="b">
@@ -897,7 +917,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>internship</t>
+          <t>job</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -913,10 +933,14 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>https://a11y.enabled.in/dpri-hiring-india-work-placement-coordinator/?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+          <t>https://jooble.org/desc/-5594253570727084532?ckey=PWD+disability+deaf+hearing+impaired+jobs&amp;rgn=55126&amp;pos=7&amp;groupId=40165&amp;elckey=7700453530903112052&amp;p=1&amp;aq=-4535327467038468568&amp;cid=12571&amp;jobAge=409&amp;brelb=100&amp;bscr=4.063623&amp;scr=4.063623</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -926,19 +950,19 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Description: Disability Rights Promotion International</t>
+          <t>&amp;nbsp;...wins have outsized impact Think you’re a good fit for this &lt;b&gt;job?&lt;/b&gt; Tell us more about yourself and why you're interested in the...&amp;nbsp;&amp;nbsp;...national origin, gender, gender identity, sexual orientation, protected veteran status, &lt;b&gt;disability,&lt;/b&gt; age, or other legally protected sta</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DEI / LGBTQIA + Person with disability - Public Relations Intern</t>
+          <t>Senior Manager TreasuryOps</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Burson</t>
+          <t>Falconx</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -951,7 +975,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>internship</t>
+          <t>job</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -969,12 +993,12 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>7 days ago</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.co.in/job-listing/dei-lgbtqia-person-with-disability-public-relations-intern-burson-JV_KO0,58_KE59,65.htm?jl=1009974840240&amp;utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+          <t>https://jooble.org/desc/-8392297601424111350?ckey=PWD+disability+deaf+hearing+impaired+jobs&amp;rgn=55126&amp;pos=8&amp;groupId=40165&amp;elckey=7700453530903112052&amp;p=1&amp;aq=-4535327467038468568&amp;cid=12571&amp;jobAge=1254&amp;brelb=100&amp;bscr=3.7949252&amp;scr=3.7949252</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -984,24 +1008,24 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Who we are: Burson, part of WPP, is the global communications leader built to create value for clients through reputation. With highly specialized teams, industry-leading technologies and breakthrough creative, we help brands and businesses redefine reputation as a competitive advantage so they can</t>
+          <t>&amp;nbsp;...origin, ancestry, ethnicity, sex (including gender, pregnancy, sexual orientation, and gender identity), age, physical or mental &lt;b&gt;disability,&lt;/b&gt; veteran or military status, genetic information, citizenship, or any other legally-recognized protected basis under federal, state...&amp;nbsp;</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sales Manager Kolkata (India)</t>
+          <t>Piping Designer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Divyang Bhartia</t>
+          <t>Dynamics ATS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kolkata, West Bengal</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D10" t="b">
@@ -1027,12 +1051,12 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>4 days ago</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>https://in.jobrapido.com/jobpreview/7666997820758425600?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+          <t>https://jooble.org/desc/-2515853188082520226?ckey=PWD+disability+deaf+hearing+impaired+jobs&amp;rgn=55126&amp;pos=9&amp;groupId=40165&amp;elckey=7700453530903112052&amp;p=1&amp;aq=-4535327467038468568&amp;cid=12571&amp;jobAge=1062&amp;brelb=100&amp;bscr=3.7238712&amp;scr=3.7238712</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1042,19 +1066,19 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Responsibilities Manage key partnerships, drive revenue growth. Lead strategic planning, oversee sales strategy. Drive channel sales through CRM &amp; consulting. Build robust relationships with clients &amp; partners. Perks and advantages Health insurance</t>
+          <t>&amp;nbsp;...Piping Designer &lt;b&gt;JOB-&lt;/b&gt;10046478 Anticipated Start Date 5/11/2026 Location Beaumont, TX Type of Employment...&amp;nbsp;&amp;nbsp;...color, religion, sex, sexual orientation, age, national origin, &lt;b&gt;disability,&lt;/b&gt; protected veteran status, gender identity or any other factors...&amp;nbsp;</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Trained Caregiver/ Divyang Mitra</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Composite Regional Centre for Skill Development Rehabilitation &amp; Empowerment of Persons with Disabilities (CRC-Bhopal)</t>
+          <t>Quality Talent Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1085,12 +1109,12 @@
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>3 days ago</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>https://www.aspirantai.co.in/trained-caregiver-divyang-mitra--crc-bhopal-recruitment-2026-apply-offline-for-10-nurse-physiotherapist-and-more-posts-3044069--88c76bb169a8?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+          <t>https://jooble.org/desc/-7214701894644427917?ckey=PWD+disability+deaf+hearing+impaired+jobs&amp;rgn=55126&amp;pos=10&amp;groupId=40165&amp;elckey=7700453530903112052&amp;p=1&amp;aq=-4535327467038468568&amp;cid=12571&amp;jobAge=126&amp;brelb=100&amp;bscr=3.7238712&amp;scr=3.7238712</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1100,24 +1124,24 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Qualification: MPhil, PGDRP, PDCP, Bachelor in Occupational Therapy, B.Sc, Degree in Speech and Language Sciences, BASLP, DECSE, D.Ed., B.Ed., Bachelor in Physiotherapy, Diploma or BSc Nursing, RCI/National Trust certified Course in Caregiving OR 3-year experience in caregiving of CWSN. Clinical / R</t>
+          <t>Banker &lt;b&gt;Job &lt;/b&gt;Type: Full-time, Part-time Shift: Day Shift Our client, a global trailblazer in financial services, is not...&amp;nbsp;&amp;nbsp;...~401(k) plan ~ Paid time off and parental leave ~ &lt;b&gt;Disability,&lt;/b&gt; life, critical illness, and accident insurance ~ Critical...&amp;nbsp;</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Oil India Limited PwBD Recruitment 2026 – Apply for 49 Posts</t>
+          <t>Transaction Monitoring Associate</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Oil India Limited (OIL), Ministry of Petroleum and Natural Gas, Government of India</t>
+          <t>Falconx</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D12" t="b">
@@ -1135,28 +1159,20 @@
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>₹26.6K–₹1.45L a month</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="n">
-        <v>319200</v>
-      </c>
-      <c r="M12" t="n">
-        <v>17400</v>
-      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>18 days ago</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>https://jobone.in/job/oil-india-limited-oil-india-limited-pwbd-2026-for-49-recruitment-2026?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+          <t>https://jooble.org/desc/97107214260340814?ckey=PWD+disability+deaf+hearing+impaired+jobs&amp;rgn=55126&amp;pos=11&amp;groupId=40165&amp;elckey=7700453530903112052&amp;p=1&amp;aq=-4535327467038468568&amp;cid=12571&amp;jobAge=1278&amp;brelb=100&amp;bscr=3.6998549&amp;scr=3.6998549</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1166,24 +1182,24 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Quick Info Overview OrganizationOil India Limited (OIL), Ministry of Petroleum and Natural Gas, Government of India Post NameOil India Limited PwBD Recruitment 2026 – Apply for 49 Posts Total Vacancies49 CategoryCentral Govt Jobs LocationAssam Education10th_pass, 12th_pass, diploma Age Limit40 Yrs (</t>
+          <t>&amp;nbsp;...origin, ancestry, ethnicity, sex (including gender, pregnancy, sexual orientation, and gender identity), age, physical or mental &lt;b&gt;disability,&lt;/b&gt; veteran or military status, genetic information, citizenship, or any other legally-recognized protected basis under federal, state...&amp;nbsp;</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Oil India PwBD Workperson Recruitment 2026: 49 Workperson Posts</t>
+          <t>Organizer / Union Representative - Southern CA counties</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Oil India Limited</t>
+          <t>SEIU UHW West, United Healthcare Workers West</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Duliajan, Assam</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D13" t="b">
@@ -1191,7 +1207,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>job</t>
+          <t>internship</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1203,26 +1219,26 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>₹26.6K–₹1.45L a month</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="n">
-        <v>319200</v>
-      </c>
-      <c r="M13" t="n">
-        <v>17400</v>
-      </c>
+          <t>$74k</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>74000</v>
+      </c>
+      <c r="K13" t="n">
+        <v>74000</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t>18 days ago</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>https://www.sarkarirojgarkendra.com/oil-india-pwbd-workperson-may-2026/?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+          <t>https://jooble.org/desc/8176836496905622634?ckey=PWD+disability+deaf+hearing+impaired+jobs&amp;rgn=55126&amp;pos=12&amp;groupId=40165&amp;elckey=7700453530903112052&amp;p=1&amp;aq=-4535327467038468568&amp;cid=12571&amp;jobAge=2958&amp;brelb=100&amp;bscr=3.5744443&amp;scr=3.5744443</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1232,28 +1248,28 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Oil India Limited invites online applications for 49 PwBD Workperson posts including Junior Technician, Junior Office Assistant, and Junior Engineer vacancies. Eligible candidates from Assam and Arunachal Pradesh can apply online before 08 June 2026.</t>
+          <t>&amp;nbsp;...new organizing, internal organizing, and political action. &lt;b&gt;Job &lt;/b&gt;Functions: Work with the Executive Board members, shop stewards...&amp;nbsp;&amp;nbsp;..., age, sexual orientation, marital status, religion, or &lt;b&gt;disability.&lt;/b&gt; To Apply: Go to Jobs at SEIU-UHW . WHEN APPLYING: Be...&amp;nbsp;</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Compassionate Remote Crisis Chat &amp; Text Counselor – Full‑Time Position with arenaflex Supporting Deaf, Hard‑of‑Hearing &amp; Deaf‑Plus Communities</t>
+          <t>Software Intern</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>remotepromsp</t>
+          <t>ChargePoint</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Anywhere</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1275,12 +1291,12 @@
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>5 days ago</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>https://www.mysmartpros.com/remotepro/job/1704329?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+          <t>https://jooble.org/desc/-6640696514081591739?ckey=PWD+disability+deaf+hearing+impaired+jobs&amp;rgn=55126&amp;pos=13&amp;groupId=40165&amp;elckey=7700453530903112052&amp;p=1&amp;aq=-4535327467038468568&amp;cid=12571&amp;jobAge=294&amp;brelb=100&amp;bscr=3.5596242&amp;scr=3.5596242</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1290,32 +1306,32 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>```html About arenaflex – A Mission‑Driven Non‑Profit Championing Crisis Support At arenaflex, we are dedicated to safeguarding the emotional and physical well‑being of individuals who are Deaf, Hard of Hearing, Late‑Deafened, DeafBlind, DeafDisabled, and Deaf+. Operating across Missouri and extendi</t>
+          <t>&amp;nbsp;..., gender identity, gender expression, sexual orientation, age, &lt;b&gt;disability,&lt;/b&gt; veteran status, genetic information, marital status or any legally...&amp;nbsp;&amp;nbsp;...in the application or interview process, to perform essential &lt;b&gt;job &lt;/b&gt;functions, or to access any other benefits and privi</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Urgently Require Special Education Teacher Deaf &amp; Hard of Hearing DHH (ID 2417) in San Diego, CA</t>
+          <t>Senior Software Engineer - SDK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>remotepromsp</t>
+          <t>Backtrace I/O</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Anywhere</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>internship</t>
+          <t>job</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1333,12 +1349,12 @@
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>7 days ago</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>https://www.mysmartpros.com/remotepro/job/199232?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+          <t>https://jooble.org/desc/-5295575618288970463?ckey=PWD+disability+deaf+hearing+impaired+jobs&amp;rgn=55126&amp;pos=14&amp;groupId=40165&amp;elckey=7700453530903112052&amp;p=1&amp;aq=-4535327467038468568&amp;cid=12571&amp;jobAge=6126&amp;brelb=100&amp;bscr=3.4923038&amp;scr=3.4923038</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1348,28 +1364,28 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Job title: Special Education Teacher Deaf &amp; Hard of Hearing DHH (ID 2417) Company: San Diego County Office of Education Job description: Job Summary Join our amazing team The San Diego County Office of Education is a collaborative organization that works toward a future without boundaries for our st</t>
+          <t>&amp;nbsp;...specific role. Please note our privacy terms when applying for a &lt;b&gt;job &lt;/b&gt;at Sauce Labs. Sauce Labs is proud to be an Equal...&amp;nbsp;&amp;nbsp;...status, sexual orientation, age, marital status, veteran status or &lt;b&gt;disability &lt;/b&gt;status. Security responsibilities at Sauce At Sauce, we will...</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Remote Teacher for Deaf / Hard of Hearing in Schools | WFH</t>
+          <t>Senior Financial Analyst</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>remotepromsp</t>
+          <t>Dish</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Anywhere</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1391,12 +1407,12 @@
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>5 days ago</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>https://www.mysmartpros.com/remotepro/job/442673?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+          <t>https://jooble.org/desc/2093429852574037857?ckey=PWD+disability+deaf+hearing+impaired+jobs&amp;rgn=55126&amp;pos=15&amp;groupId=40165&amp;elckey=7700453530903112052&amp;p=1&amp;aq=-4535327467038468568&amp;cid=12571&amp;jobAge=150&amp;brelb=100&amp;bscr=3.4896383&amp;scr=3.4896383</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1406,32 +1422,32 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Job Overview We are dedicated to delivering exceptional, inclusive education that empowers all students, recognizing the value of diverse learning experiences. Our mission is to cultivate an environment where students who are Deaf and Hard of Hearing can flourish. We invite passionate and qualified</t>
+          <t>&amp;nbsp;...&lt;b&gt;Job &lt;/b&gt;Description Company Summary DISH Network Technologies India Pvt. Ltd is a technology subsidiary of EchoStar. Our organization...&amp;nbsp;&amp;nbsp;..., sex, sexual orientation, gender identity, national origin, &lt;b&gt;disability,&lt;/b&gt; or protected veteran status. EchoStar will accommodate th</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Immediately Need NON-CLASSIFIED: Teacher of the Deaf: Elementary in Colorado Springs, CO</t>
+          <t>Lead Engineer - 5G Signaling</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>remotepromsp</t>
+          <t>Dish</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Anywhere</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>internship</t>
+          <t>job</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1449,12 +1465,12 @@
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>8 days ago</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>https://www.mysmartpros.com/remotepro/job/196421?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+          <t>https://jooble.org/desc/-2433996160867741743?ckey=PWD+disability+deaf+hearing+impaired+jobs&amp;rgn=55126&amp;pos=16&amp;groupId=40165&amp;elckey=7700453530903112052&amp;p=1&amp;aq=-4535327467038468568&amp;cid=12571&amp;jobAge=966&amp;brelb=100&amp;bscr=3.2406487&amp;scr=3.2406487</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1464,28 +1480,28 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Job title: NON-CLASSIFIED: Teacher of the Deaf: Elementary Company: State of Colorado Job description: Department Information Vision Statement: CSDB aspires to be an exemplary global resource for families and professionals that excels in preparing diverse learners to transform the world with PRIDE:</t>
+          <t>&amp;nbsp;...&lt;b&gt;Job &lt;/b&gt;Description Company Summary DISH Network Technologies India Pvt. Ltd is a technology subsidiary of EchoStar. Our organization...&amp;nbsp;&amp;nbsp;..., sex, sexual orientation, gender identity, national origin, &lt;b&gt;disability,&lt;/b&gt; or protected veteran status. EchoStar will accommodate th</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>[Remote-Position] Looking for WLMS ParaEducator, Deaf /Hard of</t>
+          <t>Data Engineering Manager</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>remotepromsp</t>
+          <t>Galaxy</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Anywhere</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1507,12 +1523,12 @@
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>8 days ago</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>https://www.mysmartpros.com/remotepro/job/829755?utm_campaign=google_jobs_apply&amp;utm_source=google_jobs_apply&amp;utm_medium=organic</t>
+          <t>https://jooble.org/desc/-5015276982819041332?ckey=PWD+disability+deaf+hearing+impaired+jobs&amp;rgn=55126&amp;pos=17&amp;groupId=40165&amp;elckey=7700453530903112052&amp;p=1&amp;aq=-4535327467038468568&amp;cid=12571&amp;jobAge=1086&amp;brelb=100&amp;bscr=3.227951&amp;scr=3.227951</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -1522,7 +1538,5849 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Quick Overview:Position: Looking For WLMS Paraeducator, Deaf /hard Of HearingCompany: Thornton, COLocation: RemoteStart Date: Immediate openings availableCompensation: a competitive salaryÂ Â Job title: WLMS ParaEducator, Deaf /Hard of Hearing Company: Adams County School District 12 Job description</t>
+          <t>&amp;nbsp;...to provide equal employment opportunities to all employees and &lt;b&gt;job &lt;/b&gt;applicants for employment without regard to actual or perceived...&amp;nbsp;&amp;nbsp;...caregiver status, ancestry, national origin, citizenship status, &lt;b&gt;disability,&lt;/b&gt; military or veteran status, protected medical condit</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Community Mobilization Specialist</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Gang Alternative, Inc</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D19" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>$40k - $45k</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>40000</v>
+      </c>
+      <c r="M19" t="n">
+        <v>40000</v>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>https://jooble.org/jdp/7292593580202955346?ckey=PWD+disability+deaf+hearing+impaired+jobs&amp;rgn=55126&amp;pos=18&amp;groupId=40165&amp;elckey=7700453530903112052&amp;p=1&amp;aq=-4535327467038468568&amp;cid=12571&amp;jobAge=263&amp;brelb=100&amp;bscr=3.227951&amp;scr=3.227951</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...Equal Opportunity employer. Personnel are chosen based on ability without regard to race, color, religion, sex, national origin, &lt;b&gt;disability,&lt;/b&gt; marital status or sexual orientation, in accordance with federal and state law. Gang Alternative, Inc. is a Drug-Free Workplace....&amp;nbsp;</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Manager - Public Policy and Advocacy</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>InMobi</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-8063637637931729603?ckey=PWD+disability+deaf+hearing+impaired+jobs&amp;rgn=55126&amp;pos=20&amp;groupId=40165&amp;elckey=7700453530903112052&amp;p=1&amp;aq=-4535327467038468568&amp;cid=12571&amp;jobAge=6870&amp;brelb=100&amp;bscr=3.1144543&amp;scr=3.1144543</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...situations within dynamic commercial and policy environments. &lt;b&gt;Job &lt;/b&gt;responsibilities Develop policy positions on economic...&amp;nbsp;&amp;nbsp;...providing reasonable accommodations to qualified individuals with &lt;b&gt;disabilities &lt;/b&gt;throughout the hiring process and in the workplace. Visit to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Lead Network Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dish</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/1651805079965356562?ckey=PWD+disability+deaf+hearing+impaired+jobs&amp;rgn=55126&amp;pos=21&amp;groupId=40165&amp;elckey=7700453530903112052&amp;p=2&amp;aq=-2378177118970145297&amp;cid=12571&amp;jobAge=486&amp;brelb=100&amp;bscr=3.052236&amp;scr=3.052236</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...&lt;b&gt;Job &lt;/b&gt;Description Company Summary DISH Network Technologies India Pvt. Ltd is a technology subsidiary of EchoStar. Our organization...&amp;nbsp;&amp;nbsp;..., sex, sexual orientation, gender identity, national origin, &lt;b&gt;disability,&lt;/b&gt; or protected veteran status. EchoStar will accommodate th</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Lead Engineer - Cloud Reliability Engineering</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dish</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D22" t="b">
+        <v>0</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-6392192563862781244?ckey=PWD+disability+deaf+hearing+impaired+jobs&amp;rgn=55126&amp;pos=22&amp;groupId=40165&amp;elckey=7700453530903112052&amp;p=2&amp;aq=-2378177118970145297&amp;cid=12571&amp;jobAge=486&amp;brelb=100&amp;bscr=2.8628097&amp;scr=2.8628097</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...&lt;b&gt;Job &lt;/b&gt;Description Company Summary DISH Network Technologies India Pvt. Ltd is a technology subsidiary of EchoStar. Our organization...&amp;nbsp;&amp;nbsp;..., sex, sexual orientation, gender identity, national origin, &lt;b&gt;disability,&lt;/b&gt; or protected veteran status. EchoStar will accommodate th</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Staff Engineer (Full Stack)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>The Block</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D23" t="b">
+        <v>0</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-1018388704434660749?ckey=PWD+disability+deaf+hearing+impaired+jobs&amp;rgn=55126&amp;pos=23&amp;groupId=40165&amp;elckey=7700453530903112052&amp;p=2&amp;aq=-2378177118970145297&amp;cid=12571&amp;jobAge=558&amp;brelb=100&amp;bscr=2.5439658&amp;scr=2.5439658</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...The Block does not sponsor US work authorizations for this &lt;b&gt;job &lt;/b&gt;position including H-1B, O-1, and TN. The Block also does not hire...&amp;nbsp;&amp;nbsp;...sexual orientation, gender identity, national origin, veteran, or &lt;b&gt;disability &lt;/b&gt;status. Pursuant to applicable pay transparency laws,</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Software Intern</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ChargePoint</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D24" t="b">
+        <v>0</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>internship</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-6640696514081591739?ckey=speech+impaired+specially+abled+jobs+internship&amp;rgn=55126&amp;pos=1&amp;groupId=35087&amp;elckey=-1309547180055708938&amp;p=1&amp;aq=8963562265231688525&amp;cid=12571&amp;jobAge=294&amp;brelb=100&amp;bscr=14.922876&amp;scr=14.922876</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...employment process. If you need a reasonable accommodation to participate in the application or interview process, to perform essential &lt;b&gt;job &lt;/b&gt;functions, or to access any other benefits and privileges of employment, please contact us at ****@*****.*** ....&amp;nbsp;</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Windows Systems Administrator DevOps</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>The Computer Merchant, Ltd</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Brighton, NY</t>
+        </is>
+      </c>
+      <c r="D25" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>$36.54k - $80.18k</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>36540</v>
+      </c>
+      <c r="M25" t="n">
+        <v>36540</v>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-4571592217804903503?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=1&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=1&amp;aq=3195850673672882888&amp;cid=12571&amp;jobAge=30&amp;brelb=100&amp;bscr=97.45947&amp;scr=97.45947</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...probation and training period, with about half the time potentially &lt;b&gt;remote &lt;/b&gt;afterward; local candidates are preferred. We offer medical,...&amp;nbsp;&amp;nbsp;...care flexible spending, a 401(k) plan, voluntary life and &lt;b&gt;disability &lt;/b&gt;options, employee assistance support, and sick leave in</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CFO Consultant</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Burkland</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="D26" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/1019274786811447600?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=4&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=1&amp;aq=3195850673672882888&amp;cid=12571&amp;jobAge=6654&amp;brelb=100&amp;bscr=87.12007&amp;scr=87.12007</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...clients and happy employees. We are a &lt;b&gt;remote-&lt;/b&gt;first company with over 180 incredible team...&amp;nbsp;&amp;nbsp;...and look forward to the parts of your &lt;b&gt;job &lt;/b&gt;that require analytical thinking and planning...&amp;nbsp;&amp;nbsp;...your dependents. ~ Short &amp; Long Term &lt;b&gt;Disability &lt;/b&gt;Insurance t</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Recruiter (Work From Home/Commission)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Gpac</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Spencer County, IN</t>
+        </is>
+      </c>
+      <c r="D27" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/1309236068599077061?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=5&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=1&amp;aq=3195850673672882888&amp;cid=12571&amp;jobAge=2574&amp;brelb=100&amp;bscr=85.811806&amp;scr=85.811806</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...in the process of interviewing to add new recruiters to their &lt;b&gt;remote/&lt;/b&gt;work from home team. There's no time like the present. If you have...&amp;nbsp;&amp;nbsp;..., color, sex (including pregnancy), religion, national origin, &lt;b&gt;disability,&lt;/b&gt; sexual orientation, gender identity, marital stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Financial Management Services (FMS) Coordinator - Self Determination</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>HR Alliance</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="D28" t="b">
+        <v>1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>$70k - $80k</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="n">
+        <v>70000</v>
+      </c>
+      <c r="M28" t="n">
+        <v>70000</v>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-6496245237225281533?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=6&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=1&amp;aq=3195850673672882888&amp;cid=12571&amp;jobAge=4241&amp;brelb=110&amp;bscr=82.06915&amp;scr=82.06915</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...&lt;b&gt;Job &lt;/b&gt;Description: Financial Management Services (FMS) Coordinator – California Self-Determination...&amp;nbsp;&amp;nbsp;...Program Location: California (&lt;b&gt;remote/&lt;/b&gt;onsite) Reports To: FMS Program...&amp;nbsp;&amp;nbsp;...Experience in social services, fiscal management, &lt;b&gt;disability &lt;/b&gt;services,</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Controller (Remote)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Nurp</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="D29" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/5666641725136644648?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=7&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=1&amp;aq=3195850673672882888&amp;cid=12571&amp;jobAge=28&amp;brelb=100&amp;bscr=81.85655&amp;scr=81.85655</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...up to 25 pounds at times. Reasonable accommodations may be made to enable individuals with &lt;b&gt;disabilities &lt;/b&gt;to perform the essential requirements. BENEFITS ~100% &lt;b&gt;Remote &lt;/b&gt;Position ~ Paid Time Off ~ Health insurance ~ Dental Insurance ~ Vision Insurance ~ Life...&amp;nbsp;</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Regional Field Service Manager, Central</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SaintGobain</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Des Moines, IA</t>
+        </is>
+      </c>
+      <c r="D30" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>$102k - $158k</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="n">
+        <v>102000</v>
+      </c>
+      <c r="M30" t="n">
+        <v>102000</v>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/6222857850991614991?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=9&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=1&amp;aq=3195850673672882888&amp;cid=12571&amp;jobAge=50&amp;brelb=100&amp;bscr=81.17728&amp;scr=81.17728</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...technical procedures Proficient with &lt;b&gt;remote &lt;/b&gt;support tools such as RVNC Viewer...&amp;nbsp;&amp;nbsp;...identity or expression, national origin, age, &lt;b&gt;disability,&lt;/b&gt; genetic information, marital status, amnesty...&amp;nbsp;&amp;nbsp;...require pay information be provided in &lt;b&gt;job &lt;/b&gt;postings. Sa</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BMV Investigator</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>State of Ohio Jobs</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Parma, OH</t>
+        </is>
+      </c>
+      <c r="D31" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/1053063739023674649?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=11&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=1&amp;aq=3195850673672882888&amp;cid=12571&amp;jobAge=95&amp;brelb=100&amp;bscr=78.76616&amp;scr=78.76616</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...minimum qualifications outlined in this &lt;b&gt;job &lt;/b&gt;posting. 3. Respond to all questions asked...&amp;nbsp;&amp;nbsp;...weather and elements; may work in &lt;b&gt;remote &lt;/b&gt;rural or metro areas; may work in high-crime...&amp;nbsp;&amp;nbsp;...requirement of the hiring process. To request a &lt;b&gt;disability &lt;/b&gt;acco</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Product Manager in civic tech | Remote</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Last Call Media</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Boston, MA</t>
+        </is>
+      </c>
+      <c r="D32" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>$90k - $120k</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="n">
+        <v>90000</v>
+      </c>
+      <c r="M32" t="n">
+        <v>90000</v>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/7317777870476687419?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=12&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=1&amp;aq=3195850673672882888&amp;cid=12571&amp;jobAge=112&amp;brelb=110&amp;bscr=78.43167&amp;scr=78.43167</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...to $120,000 Full benefits: health, dental, vision, life and &lt;b&gt;disability &lt;/b&gt;insurance, flexible PTO Professional development and work from...&amp;nbsp;&amp;nbsp;...format. Apply with a brief application questionnaire (enter &lt;b&gt;Job &lt;/b&gt;ID 43). Last Call Media is an equal opportunity employer....&amp;n</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Home Health Insurance Team Lead Remote Work from Home</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Elara Caring</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Dallas, TX</t>
+        </is>
+      </c>
+      <c r="D33" t="b">
+        <v>1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-2877846792196926048?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=13&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=1&amp;aq=3195850673672882888&amp;cid=12571&amp;jobAge=3&amp;brelb=100&amp;bscr=78.43167&amp;scr=78.43167</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...confidentiality in the workplace ~ Reliable transportation to perform &lt;b&gt;job &lt;/b&gt;tasks You will report to the Supervisor. This is not a...&amp;nbsp;&amp;nbsp;...origin, sexual orientation, age, citizenship, marital status, &lt;b&gt;disability,&lt;/b&gt; gender, gender identity or expression, or veteran status.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Maintenance Mechanic III - 3rd Shift</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SaintGobain</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Worcester, MA</t>
+        </is>
+      </c>
+      <c r="D34" t="b">
+        <v>1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>$35.26 - $38.79 per hour</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="n">
+        <v>35</v>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-975950506435469223?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=14&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=1&amp;aq=3195850673672882888&amp;cid=12571&amp;jobAge=147&amp;brelb=100&amp;bscr=78.02183&amp;scr=78.02183</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...required to effectively complete the given &lt;b&gt;job.&lt;/b&gt; Utilizes knowledge of the...&amp;nbsp;&amp;nbsp;...identity or expression, national origin, age, &lt;b&gt;disability,&lt;/b&gt; genetic information, marital status, amnesty...&amp;nbsp;&amp;nbsp;...for roles based in Washington state or &lt;b&gt;remote &lt;/b&gt;roles that wo</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SOAR Engineer [Job ID 20260504]</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Phoenix Cyber</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT</t>
+        </is>
+      </c>
+      <c r="D35" t="b">
+        <v>1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/8435528870214012142?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=15&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=1&amp;aq=3195850673672882888&amp;cid=12571&amp;jobAge=822&amp;brelb=100&amp;bscr=77.93135&amp;scr=77.93135</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...SOAR Consultant to support a commercial client. This is a 100% &lt;b&gt;remote,&lt;/b&gt; work-from-home position anywhere in the continental United States...&amp;nbsp;&amp;nbsp;..., sex, sexual orientation, gender identity, national origin, &lt;b&gt;disability,&lt;/b&gt; and/or veteran status. Phoenix Cyber participates</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Financial Accounting Manager - Supply Chain Mgmt P2P</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>West Des Moines, IA</t>
+        </is>
+      </c>
+      <c r="D36" t="b">
+        <v>1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/4940349931376304916?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=16&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=1&amp;aq=3195850673672882888&amp;cid=12571&amp;jobAge=54&amp;brelb=100&amp;bscr=76.40893&amp;scr=76.40893</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...in accounting or finance, CPA a plus &lt;b&gt;Job &lt;/b&gt;Expectations: Ability to travel up to...&amp;nbsp;&amp;nbsp;...schedule with 3 days in office and 2 days &lt;b&gt;remote &lt;/b&gt; This position is not eligible for Visa...&amp;nbsp;&amp;nbsp;..., gender identity, national origin, &lt;b&gt;disability,&lt;/b&gt; status as a protecte</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Remote Sales/Recruiting</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Gpac</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Hartford, CT</t>
+        </is>
+      </c>
+      <c r="D37" t="b">
+        <v>1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-3467850761988406763?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=17&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=1&amp;aq=3195850673672882888&amp;cid=12571&amp;jobAge=2910&amp;brelb=100&amp;bscr=76.24586&amp;scr=76.24586</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...a passion for helping people. We provide &lt;b&gt;remote &lt;/b&gt;training and support to work from your home...&amp;nbsp;&amp;nbsp;...with clients, hiring managers, and &lt;b&gt;job &lt;/b&gt;candidates Proactive in problem-solving...&amp;nbsp;&amp;nbsp;...including pregnancy), religion, national origin, &lt;b&gt;disability,&lt;/b&gt; sexu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Tax Manager (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Ashley Bowler &amp; Co.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Long Beach, CA</t>
+        </is>
+      </c>
+      <c r="D38" t="b">
+        <v>1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>$145k - $220k</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="n">
+        <v>145000</v>
+      </c>
+      <c r="M38" t="n">
+        <v>145000</v>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-1769061999380226472?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=19&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=1&amp;aq=3195850673672882888&amp;cid=12571&amp;jobAge=4&amp;brelb=100&amp;bscr=76.24586&amp;scr=76.24586</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...California requires a strong Tax Manager to work &lt;b&gt;remotely &lt;/b&gt; . The suitable candidate will handle a...&amp;nbsp;&amp;nbsp;...CPA certificate is really mandatory.. &lt;b&gt;Job &lt;/b&gt;Type: Full-time Pay: $145,000.00 - $22...&amp;nbsp;&amp;nbsp;...: ~401(k) ~ Dental insurance ~ &lt;b&gt;Disability &lt;/b&gt;insurance ~ Fle</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Civil Engineer EIT</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Gpac</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Portland, OR</t>
+        </is>
+      </c>
+      <c r="D39" t="b">
+        <v>1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>$70k - $95k</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="n">
+        <v>70000</v>
+      </c>
+      <c r="M39" t="n">
+        <v>70000</v>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-469566797880527444?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=20&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=1&amp;aq=3195850673672882888&amp;cid=12571&amp;jobAge=2814&amp;brelb=100&amp;bscr=76.208275&amp;scr=76.208275</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Now offering Work-From-Home/&lt;b&gt;Remote &lt;/b&gt;work! Come work in a dynamic environment where people are inspired to produce high quality work...&amp;nbsp;&amp;nbsp;..., color, sex (including pregnancy), religion, national origin, &lt;b&gt;disability,&lt;/b&gt; sexual orientation, gender identity, marital status, military..</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Home-Based Customer Service Positions with Competitive Pay Rates</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>NoGigiddy</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>El Paso, TX</t>
+        </is>
+      </c>
+      <c r="D40" t="b">
+        <v>1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>$19 per hour</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="n">
+        <v>19</v>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-6700699062966015295?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=22&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=2&amp;aq=-1116864549284985292&amp;cid=12571&amp;jobAge=3151&amp;brelb=110&amp;bscr=75.805466&amp;scr=75.805466</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...&lt;b&gt;Remote &lt;/b&gt;Customer Service Agent – $19/hr Start, No Degree Required Do you have a knack for resolving issues and a passion for providing...&amp;nbsp;&amp;nbsp;...of race, religion, color, national origin, gender, sexual orientation, age, marital status, veteran status, or &lt;b&gt;disability &lt;/b&gt;stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Immediate Opening: Remote Customer Service Representative with Competitive Pay</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>NoGigiddy</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Virginia Beach, VA</t>
+        </is>
+      </c>
+      <c r="D41" t="b">
+        <v>1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>$19 per hour</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="n">
+        <v>19</v>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-8623295523605085505?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=23&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=2&amp;aq=-1116864549284985292&amp;cid=12571&amp;jobAge=7246&amp;brelb=110&amp;bscr=75.75615&amp;scr=75.75615</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...We are on the lookout for enthusiastic individuals to join our &lt;b&gt;remote &lt;/b&gt;customer service team. This role involves interacting with a wide...&amp;nbsp;&amp;nbsp;...of race, religion, color, national origin, gender, sexual orientation, age, marital status, veteran status, or &lt;b&gt;disability &lt;/b&gt;st</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Trial Attorney</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Gpac</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Macon, GA</t>
+        </is>
+      </c>
+      <c r="D42" t="b">
+        <v>1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>$120k - $180k</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="n">
+        <v>120000</v>
+      </c>
+      <c r="M42" t="n">
+        <v>120000</v>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-7903017610177712302?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=24&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=2&amp;aq=-1116864549284985292&amp;cid=12571&amp;jobAge=3006&amp;brelb=100&amp;bscr=74.17857&amp;scr=74.17857</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...Attorney licensed in Georgia to join our litigation team. This is a &lt;b&gt;remote &lt;/b&gt;position , offering flexibility and the opportunity to work...&amp;nbsp;&amp;nbsp;..., color, sex (including pregnancy), religion, national origin, &lt;b&gt;disability,&lt;/b&gt; sexual orientation, gender identity, marital statu</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Audit Senior</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Gpac</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Quincy, MA</t>
+        </is>
+      </c>
+      <c r="D43" t="b">
+        <v>1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>$60k - $100k</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="n">
+        <v>60000</v>
+      </c>
+      <c r="M43" t="n">
+        <v>60000</v>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-4519126681304290517?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=28&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=2&amp;aq=-1116864549284985292&amp;cid=12571&amp;jobAge=2478&amp;brelb=100&amp;bscr=73.8916&amp;scr=73.8916</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...00-$100,000 Excellent benefits package &lt;b&gt;Job &lt;/b&gt;Type : Full-time Pay : $60,,000 Benefits : 401(k), Dental Insurance, &lt;b&gt;Disability &lt;/b&gt;Insurance, Flexible schedule, Health Insurance...&amp;nbsp;&amp;nbsp;...CPA License (Preferred) Work Location : &lt;b&gt;Remote &lt;/b&gt;/ Hybrid / On-Sight If you are inter</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>EXPERIENCED TOP-TIER FREIGHT BROKER - WORK FROM HOME(REMOTE)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Gpac</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Miami, FL</t>
+        </is>
+      </c>
+      <c r="D44" t="b">
+        <v>1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>$70k - $125k</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="n">
+        <v>70000</v>
+      </c>
+      <c r="M44" t="n">
+        <v>70000</v>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/2396642108545148324?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=29&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=2&amp;aq=-1116864549284985292&amp;cid=12571&amp;jobAge=2694&amp;brelb=100&amp;bscr=73.8916&amp;scr=73.8916</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...paid at the top of the market - keep reading. THE ROLE * 100% &lt;b&gt;remote &lt;/b&gt;/ work from home * Full cradle-to-grave brokerage *...&amp;nbsp;&amp;nbsp;..., color, sex (including pregnancy), religion, national origin, &lt;b&gt;disability,&lt;/b&gt; sexual orientation, gender identity, marital status, military...</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Biotech Project Leadership - Clinical Trials - Home- Based - (Future Needs)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="D45" t="b">
+        <v>1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-3649414612205479779?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=30&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=2&amp;aq=-1116864549284985292&amp;cid=12571&amp;jobAge=1398&amp;brelb=100&amp;bscr=73.852066&amp;scr=73.852066</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...possess superior interpersonal and organizational skills. #LI-&lt;b&gt;REMOTE &lt;/b&gt; EEO Disclaimer Parexel is an...&amp;nbsp;&amp;nbsp;...States includes race, color, religion, sex, sexual orientation, gender identity, national origin, &lt;b&gt;disability,&lt;/b&gt; or protected veteran status....&amp;nbsp;</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Entry Level Recruiter</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>gpac</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Blue Springs, MO</t>
+        </is>
+      </c>
+      <c r="D46" t="b">
+        <v>1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>$30k</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="n">
+        <v>30000</v>
+      </c>
+      <c r="M46" t="n">
+        <v>30000</v>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-1181216734819655065?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=31&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=2&amp;aq=-1116864549284985292&amp;cid=12571&amp;jobAge=438&amp;brelb=100&amp;bscr=73.62408&amp;scr=73.62408</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...motivated individuals to partner with as fully &lt;b&gt;remote &lt;/b&gt;Search Consultants. Our company was...&amp;nbsp;&amp;nbsp;...relationships with clients, hiring managers, and &lt;b&gt;job &lt;/b&gt;candidates Partner with clients to...&amp;nbsp;&amp;nbsp;...pregnancy), religion, national origin, &lt;b&gt;disability,&lt;/b&gt; sexual</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Sales Development Rep</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Kenect</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Pleasant Grove, UT</t>
+        </is>
+      </c>
+      <c r="D47" t="b">
+        <v>1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-7243849314978333440?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=32&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=2&amp;aq=-1116864549284985292&amp;cid=12571&amp;jobAge=150&amp;brelb=110&amp;bscr=73.035965&amp;scr=73.035965</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...are FULL-TIME IN THE OFFICE WITHOUT ANY &lt;b&gt;REMOTE/&lt;/b&gt;WFH OPTIONS AVAILABLE. What You Will Be...&amp;nbsp;&amp;nbsp;...Offers Health, Dental, Vision, Life &amp; &lt;b&gt;Disability &lt;/b&gt;Insurance Your birthday is a paid day...&amp;nbsp;&amp;nbsp;...decisions at Kenect are based on business needs, &lt;b&gt;job &lt;/b&gt;requireme</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Entry Level Remote Recruiter</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Gpac</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Joplin, MO</t>
+        </is>
+      </c>
+      <c r="D48" t="b">
+        <v>1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>$30k - $36k</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="n">
+        <v>30000</v>
+      </c>
+      <c r="M48" t="n">
+        <v>30000</v>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-869635502146338122?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=33&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=2&amp;aq=-1116864549284985292&amp;cid=12571&amp;jobAge=2934&amp;brelb=100&amp;bscr=72.37298&amp;scr=72.37298</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...motivated individuals to partner with as fully &lt;b&gt;remote &lt;/b&gt;Search Consultants. Our company was...&amp;nbsp;&amp;nbsp;...relationships with clients, hiring managers, and &lt;b&gt;job &lt;/b&gt;candidates * Partner with clients to...&amp;nbsp;&amp;nbsp;...pregnancy), religion, national origin, &lt;b&gt;disability,&lt;/b&gt; sexua</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Customer Service from Home: Contract Work at 19 Per Hour and Up</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>NoGigiddy</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Columbus, OH</t>
+        </is>
+      </c>
+      <c r="D49" t="b">
+        <v>1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>$19 per hour</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="n">
+        <v>19</v>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/2432597563654867289?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=34&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=2&amp;aq=-1116864549284985292&amp;cid=12571&amp;jobAge=7243&amp;brelb=110&amp;bscr=72.37298&amp;scr=72.37298</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...our team as Virtual Customer Service Representatives. In this &lt;b&gt;remote &lt;/b&gt;role, you'll ensure that every customer interaction is handled...&amp;nbsp;&amp;nbsp;...including race, religion, color, national origin, gender, sexual orientation, age, marital status, veteran status, or &lt;b&gt;disability &lt;/b</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Talent Community</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Medcor Inc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D50" t="b">
+        <v>1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>$17 per hour</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="n">
+        <v>17</v>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>https://jooble.org/jdp/-7221306913955070065?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=35&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=2&amp;aq=-1116864549284985292&amp;cid=12571&amp;jobAge=3112&amp;brelb=100&amp;bscr=71.95897&amp;scr=71.95897</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...offers a variety of opportunities with options that may include &lt;b&gt;remote/&lt;/b&gt;work from home positions, management and above, healthcare, IT,...&amp;nbsp;&amp;nbsp;...Medcor is a tobacco free and smoke free workplace!EOE/M/F/Vet/&lt;b&gt;Disability &lt;/b&gt; We are an equal opportunity employer and all qualif</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Remote Customer Service Positions Paying Up to 19 Per Hour Now Open</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>NoGigiddy</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Charleston, SC</t>
+        </is>
+      </c>
+      <c r="D51" t="b">
+        <v>1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>$19 per hour</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="n">
+        <v>19</v>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/8398960724553956377?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=36&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=2&amp;aq=-1116864549284985292&amp;cid=12571&amp;jobAge=7243&amp;brelb=110&amp;bscr=71.937096&amp;scr=71.937096</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...&lt;b&gt;Remote &lt;/b&gt;Customer Support Specialist – $19/hr Starting, No Degree Necessary Are you dedicated to providing exceptional customer service...&amp;nbsp;&amp;nbsp;...on race, religion, color, national origin, gender, sexual orientation, age, marital status, veteran status, or &lt;b&gt;disability &lt;/b&gt;stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Career Coach/Job Search Strategist - New York (US-based only)</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>IMPACT Group</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="D52" t="b">
+        <v>1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>$36 - $42 per hour</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="n">
+        <v>36</v>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/3852156927273639119?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=37&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=2&amp;aq=-1116864549284985292&amp;cid=12571&amp;jobAge=126&amp;brelb=100&amp;bscr=71.846565&amp;scr=71.846565</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...innovative technology, and personalized &lt;b&gt;job &lt;/b&gt;search or career development programs to...&amp;nbsp;&amp;nbsp;...time, casual (hours vary as available) and &lt;b&gt;remote &lt;/b&gt;position, approximately 15-20 hours per week...&amp;nbsp;&amp;nbsp;..., sexual orientation, gender identity, &lt;b&gt;disability,&lt;/b&gt; age,</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Veterinary Scribe Coordinator</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ScribeAmerica</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="D53" t="b">
+        <v>1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/6805945137578749776?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=38&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=2&amp;aq=-1116864549284985292&amp;cid=12571&amp;jobAge=3990&amp;brelb=100&amp;bscr=71.67761&amp;scr=71.67761</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...with a veterinarian functioning as their &lt;b&gt;remote &lt;/b&gt;personal assistant. The scribe’s role is...&amp;nbsp;&amp;nbsp;...focus on caring for their patients. This &lt;b&gt;job &lt;/b&gt;is second-to-none for direct exposure to...&amp;nbsp;&amp;nbsp;...and/or expression, national origin, age, &lt;b&gt;disability,&lt;/b&gt; genetics</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Telemedicine Nurse Practitioner or Physician Assistant (Sleep Medicine) - Remote</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Medbridge Healthcare</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Brentwood, TN</t>
+        </is>
+      </c>
+      <c r="D54" t="b">
+        <v>1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-1642854345906398830?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=39&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=2&amp;aq=-1116864549284985292&amp;cid=12571&amp;jobAge=366&amp;brelb=100&amp;bscr=71.11888&amp;scr=71.11888</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...Telemedicine Nurse Practitioner or Physician Assistant (Sleep Medicine) – &lt;b&gt;Remote &lt;/b&gt;⭐ Integrated Sleep Care | A MedBridge Healthcare Company...&amp;nbsp;&amp;nbsp;...protected veteran, or status as a qualified individual with a &lt;b&gt;disability.&lt;/b&gt; · AFFIRMATIVE ACTION PLAN (AAP): The Affirmative</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Start Your Home-Based Customer Service Career - Up to 19 Per Hour</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>NoGigiddy</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Center Point, AL</t>
+        </is>
+      </c>
+      <c r="D55" t="b">
+        <v>1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>$19 per hour</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="n">
+        <v>19</v>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-4190979500582072004?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=41&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=3&amp;aq=4274228925135500851&amp;cid=12571&amp;jobAge=7243&amp;brelb=110&amp;bscr=70.36177&amp;scr=70.36177</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...&lt;b&gt;Remote &lt;/b&gt;Customer Support Advisor – $19/hr, No Degree Required Are you adept at providing exceptional customer service and solving...&amp;nbsp;&amp;nbsp;...based on race, religion, color, national origin, gender, sexual orientation, age, marital status, veteran status, or &lt;b&gt;disability &lt;/b&gt;sta</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Start a Remote Customer Service Job Paying 19 Per Hour</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>NoGigiddy</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Charlotte, NC</t>
+        </is>
+      </c>
+      <c r="D56" t="b">
+        <v>1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>$19 per hour</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="n">
+        <v>19</v>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-6007190200209507103?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=42&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=3&amp;aq=4274228925135500851&amp;cid=12571&amp;jobAge=6631&amp;brelb=110&amp;bscr=70.21592&amp;scr=70.21592</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...&lt;b&gt;Remote &lt;/b&gt;Customer Support Opportunity – Start at $19/hr, No Degree Required Are you enthusiastic about providing exceptional customer...&amp;nbsp;&amp;nbsp;...on race, religion, color, national origin, gender, sexual orientation, age, marital status, veteran status, or &lt;b&gt;disability &lt;/b&gt;status</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Custodian-2</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Boyd Gaming</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Opelousas, LA</t>
+        </is>
+      </c>
+      <c r="D57" t="b">
+        <v>1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/1092947577718798160?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=43&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=3&amp;aq=4274228925135500851&amp;cid=12571&amp;jobAge=222&amp;brelb=100&amp;bscr=70.098854&amp;scr=70.098854</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...sexual orientation gender identity status as a veteran and basis of &lt;b&gt;disability &lt;/b&gt;or any other federal state or local protected class. Boyd...&amp;nbsp;&amp;nbsp;...of disability or any other federal state or local protected class. &lt;b&gt;Remote &lt;/b&gt;Work : No Employment Type : Full-time...&amp;nbsp;</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Remote Customer Service Positions Paying Up to 19 Per Hour Now Open</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>NoGigiddy</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Oklahoma City, OK</t>
+        </is>
+      </c>
+      <c r="D58" t="b">
+        <v>1</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>$19 per hour</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="n">
+        <v>19</v>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/3927726865394025887?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=44&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=3&amp;aq=4274228925135500851&amp;cid=12571&amp;jobAge=7243&amp;brelb=110&amp;bscr=69.28269&amp;scr=69.28269</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...Join Our Team as a &lt;b&gt;Remote &lt;/b&gt;Customer Service Specialist – Starting at $19/hr, No Formal Education Required Are you passionate about...&amp;nbsp;&amp;nbsp;...based on race, religion, color, national origin, gender, sexual orientation, age, marital status, veteran status, or &lt;b&gt;disability &lt;/b&gt;st</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Associate QA/QC Inspector - Senior QA/QC Inspector</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Halliburton</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Duncan, OK</t>
+        </is>
+      </c>
+      <c r="D59" t="b">
+        <v>1</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/6810933734563663314?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=45&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=3&amp;aq=4274228925135500851&amp;cid=12571&amp;jobAge=222&amp;brelb=100&amp;bscr=68.74&amp;scr=68.74</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...on Fridays based on business needs. &lt;b&gt;Job &lt;/b&gt;Duties Under direct supervision,...&amp;nbsp;&amp;nbsp;...service plug containers, commanders, and &lt;b&gt;remote &lt;/b&gt;connectors, and conduct high and low-pressure...&amp;nbsp;&amp;nbsp;...without regard to race, color, religion, &lt;b&gt;disability,&lt;/b&gt; genetic informat</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>RVP of Sales</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Hyro</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="D60" t="b">
+        <v>1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/4879703938039410720?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=46&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=3&amp;aq=4274228925135500851&amp;cid=12571&amp;jobAge=126&amp;brelb=100&amp;bscr=68.59663&amp;scr=68.59663</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...teammate, we want to hear from you! This is a &lt;b&gt;remote &lt;/b&gt;role working from home with up to 50%...&amp;nbsp;&amp;nbsp;...not discriminate against any employee or &lt;b&gt;job &lt;/b&gt;applicant on the basis of race, color,...&amp;nbsp;&amp;nbsp;..., national origin, age, religion, creed, &lt;b&gt;disability &lt;/b&gt;or sex. R</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Home-Based Customer Service Jobs Starting at 19 Per Hour</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>NoGigiddy</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Kansas City, MO</t>
+        </is>
+      </c>
+      <c r="D61" t="b">
+        <v>1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>$19 per hour</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="n">
+        <v>19</v>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-2886007593937193452?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=47&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=3&amp;aq=4274228925135500851&amp;cid=12571&amp;jobAge=7243&amp;brelb=110&amp;bscr=68.47828&amp;scr=68.47828</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...&lt;b&gt;Remote &lt;/b&gt;Customer Service Role – Start at $19/hr, No Academic Requirements Do you have a knack for assisting others and solving problems...&amp;nbsp;&amp;nbsp;...race, religion, color, national origin, gender, sexual orientation, age, marital status, veteran status, or &lt;b&gt;disability &lt;/b&gt;status</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Senior Enterprise Account Manager</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Hyro</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="D62" t="b">
+        <v>1</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/5079707088772858421?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=48&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=3&amp;aq=4274228925135500851&amp;cid=12571&amp;jobAge=150&amp;brelb=100&amp;bscr=68.46207&amp;scr=68.46207</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...levels within health systems. This is a &lt;b&gt;remote &lt;/b&gt;role working from home with up to 50%...&amp;nbsp;&amp;nbsp;...not discriminate against any employee or &lt;b&gt;job &lt;/b&gt;applicant on the basis of race, color, gender...&amp;nbsp;&amp;nbsp;..., national origin, age, religion, creed, &lt;b&gt;disability &lt;/b&gt;or sex.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Civil Litigation Attorney</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Gpac</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Asheville, NC</t>
+        </is>
+      </c>
+      <c r="D63" t="b">
+        <v>1</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-5633280540320438675?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=50&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=3&amp;aq=4274228925135500851&amp;cid=12571&amp;jobAge=3102&amp;brelb=100&amp;bscr=68.46207&amp;scr=68.46207</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Job &lt;/b&gt;Description Great opportunity for an experienced civil litigator to join an existing...&amp;nbsp;&amp;nbsp;...Environment: Indoor Office Setting &lt;b&gt;Remote &lt;/b&gt;work capabilities provided as needed...&amp;nbsp;&amp;nbsp;...Medical, Dental, and Vision Life, Short-term &lt;b&gt;Disability,&lt;/b&gt; and Long-term Disabi</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Litigation Attorney</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Gpac</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Mcminnville, OR</t>
+        </is>
+      </c>
+      <c r="D64" t="b">
+        <v>1</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>$100k - $150k</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="n">
+        <v>100000</v>
+      </c>
+      <c r="M64" t="n">
+        <v>100000</v>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/159040815264815614?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=51&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=3&amp;aq=4274228925135500851&amp;cid=12571&amp;jobAge=2646&amp;brelb=100&amp;bscr=67.90517&amp;scr=67.90517</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...resources, and support staff * Onsite work preferred, potential for &lt;b&gt;remote &lt;/b&gt;work periodically This is an exceptional opportunity to join...&amp;nbsp;&amp;nbsp;..., color, sex (including pregnancy), religion, national origin, &lt;b&gt;disability,&lt;/b&gt; sexual orientation, gender identity, marital stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Remote Insurance Defense Attorney</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Gpac</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Irvine, CA</t>
+        </is>
+      </c>
+      <c r="D65" t="b">
+        <v>1</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>$120k - $200k</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="n">
+        <v>120000</v>
+      </c>
+      <c r="M65" t="n">
+        <v>120000</v>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/5177797037041639205?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=52&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=3&amp;aq=4274228925135500851&amp;cid=12571&amp;jobAge=2478&amp;brelb=100&amp;bscr=67.90517&amp;scr=67.90517</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...experience level Work Environment: Hybrid or can be fully &lt;b&gt;remote &lt;/b&gt;work Collaborative team-based law firm and support staff Compensation...&amp;nbsp;&amp;nbsp;..., color, sex (including pregnancy), religion, national origin, &lt;b&gt;disability,&lt;/b&gt; sexual orientation, gender identity, marital statu</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Worker's Compensation Attorney</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Gpac</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Huntington, WV</t>
+        </is>
+      </c>
+      <c r="D66" t="b">
+        <v>1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>$100k - $130k</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="n">
+        <v>100000</v>
+      </c>
+      <c r="M66" t="n">
+        <v>100000</v>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/7904362015393254415?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=53&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=3&amp;aq=4274228925135500851&amp;cid=12571&amp;jobAge=2766&amp;brelb=100&amp;bscr=67.90517&amp;scr=67.90517</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>A growing firm is seeking a &lt;b&gt;REMOTE &lt;/b&gt;(NJ licensed) Worker's Compensation Attorney If you are an attorney looking for a long-term opportunity...&amp;nbsp;&amp;nbsp;..., color, sex (including pregnancy), religion, national origin, &lt;b&gt;disability,&lt;/b&gt; sexual orientation, gender identity, marital status, mi</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Audit Manager (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Gpac</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Houston, TX</t>
+        </is>
+      </c>
+      <c r="D67" t="b">
+        <v>1</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>$120k - $160k</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="n">
+        <v>120000</v>
+      </c>
+      <c r="M67" t="n">
+        <v>120000</v>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-8791931573900744578?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=54&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=3&amp;aq=4274228925135500851&amp;cid=12571&amp;jobAge=2742&amp;brelb=100&amp;bscr=67.90517&amp;scr=67.90517</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>If you are a proven and experienced Hybrid/&lt;b&gt;Remote &lt;/b&gt;Audit Manager who can add your expertise to a Top Local CPA firm, a great opportunity...&amp;nbsp;&amp;nbsp;..., color, sex (including pregnancy), religion, national origin, &lt;b&gt;disability,&lt;/b&gt; sexual orientation, gender identity, marital status, milit</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Hybrid Tax Manager</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Gpac</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="D68" t="b">
+        <v>1</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>$120k - $160k</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="n">
+        <v>120000</v>
+      </c>
+      <c r="M68" t="n">
+        <v>120000</v>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/3240166150526737639?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=55&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=3&amp;aq=4274228925135500851&amp;cid=12571&amp;jobAge=2742&amp;brelb=100&amp;bscr=67.7791&amp;scr=67.7791</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...to the recent growth of the firm, there is an opportunity for a &lt;b&gt;Remote &lt;/b&gt;Tax Manager to join a team of highly motivated staff. Tax...&amp;nbsp;&amp;nbsp;..., color, sex (including pregnancy), religion, national origin, &lt;b&gt;disability,&lt;/b&gt; sexual orientation, gender identity, marital status, mil</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Attorney - Corporate Associate</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Dauntless Discovery</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Rochester, NY</t>
+        </is>
+      </c>
+      <c r="D69" t="b">
+        <v>1</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>$120k - $170k</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="n">
+        <v>120000</v>
+      </c>
+      <c r="M69" t="n">
+        <v>120000</v>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/2733176078330883760?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=56&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=3&amp;aq=4274228925135500851&amp;cid=12571&amp;jobAge=1134&amp;brelb=100&amp;bscr=67.7791&amp;scr=67.7791</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...&lt;b&gt;REMOTE &lt;/b&gt;POSITION Our client, a regional east coast corporate law firm is seeking a securities and capital markets associate attorney...&amp;nbsp;&amp;nbsp;..., national origin, sex, age, marital status, sexual orientation, &lt;b&gt;disability,&lt;/b&gt; veteran status or any other illegal consideration..</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Hybrid/Remote Tax Supervisor</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Gpac</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Richardson, TX</t>
+        </is>
+      </c>
+      <c r="D70" t="b">
+        <v>1</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>$105k - $125k</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="n">
+        <v>105000</v>
+      </c>
+      <c r="M70" t="n">
+        <v>105000</v>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/3013988591694316504?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=57&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=3&amp;aq=4274228925135500851&amp;cid=12571&amp;jobAge=2742&amp;brelb=100&amp;bscr=67.744415&amp;scr=67.744415</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...: * $105,000-$125,000 * Excellent benefits package * Hyrbid &lt;b&gt;Remote &lt;/b&gt;role To be considered, please apply with a resume. If you have...&amp;nbsp;&amp;nbsp;..., color, sex (including pregnancy), religion, national origin, &lt;b&gt;disability,&lt;/b&gt; sexual orientation, gender identity, marital status, mi</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Audit Senior Associate (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Gpac</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Dallas, TX</t>
+        </is>
+      </c>
+      <c r="D71" t="b">
+        <v>1</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>$80k - $100k</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="n">
+        <v>80000</v>
+      </c>
+      <c r="M71" t="n">
+        <v>80000</v>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/99132147174172481?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=58&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=3&amp;aq=4274228925135500851&amp;cid=12571&amp;jobAge=2742&amp;brelb=100&amp;bscr=67.66863&amp;scr=67.66863</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...Base Salary: $75,000-$105,000 * Full benefits package * Hybrid/&lt;b&gt;Remote &lt;/b&gt; To be considered, please apply with a resume. If you have any...&amp;nbsp;&amp;nbsp;..., color, sex (including pregnancy), religion, national origin, &lt;b&gt;disability,&lt;/b&gt; sexual orientation, gender identity, marital status,</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Partnerships Program Specialist</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Otto</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="D72" t="b">
+        <v>1</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>$73k</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="n">
+        <v>73000</v>
+      </c>
+      <c r="M72" t="n">
+        <v>73000</v>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-5553545578355085309?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=59&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=3&amp;aq=4274228925135500851&amp;cid=12571&amp;jobAge=582&amp;brelb=100&amp;bscr=67.53895&amp;scr=67.53895</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...re signed up. Enrollment is only half the &lt;b&gt;job &lt;/b&gt;— you'll also drive each practice to...&amp;nbsp;&amp;nbsp;...00/yr (OTE: $73,000/yr) plus benefits &lt;b&gt;Remote,&lt;/b&gt; US-based. Austin, TX preferred. At Otto...&amp;nbsp;&amp;nbsp;...policy Life insurance, short and longterm &lt;b&gt;disability &lt;/b&gt;insurance Empl</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Discover a Flexible Customer Service Role with Pay Starting at 19 Per Hour</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>NoGigiddy</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL</t>
+        </is>
+      </c>
+      <c r="D73" t="b">
+        <v>1</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>$19 per hour</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="n">
+        <v>19</v>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-4603224105739710016?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=60&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=3&amp;aq=4274228925135500851&amp;cid=12571&amp;jobAge=7243&amp;brelb=110&amp;bscr=67.05693&amp;scr=67.05693</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...&lt;b&gt;Remote &lt;/b&gt;Customer Assistance Agent – $19/hr Start, No Degree Required Are you a compassionate individual who loves helping others and...&amp;nbsp;&amp;nbsp;...race, religion, color, national origin, gender, sexual orientation, age, marital status, veteran status, or &lt;b&gt;disability &lt;/b&gt;status. #</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Family Law Attorney</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>PSI</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Spokane, WA</t>
+        </is>
+      </c>
+      <c r="D74" t="b">
+        <v>1</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/3661974276355520236?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=61&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=4&amp;aq=-2800508538475755211&amp;cid=12571&amp;jobAge=918&amp;brelb=110&amp;bscr=67.05693&amp;scr=67.05693</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...Law Attorney to join our legal team in Washington state. It is a &lt;b&gt;remote &lt;/b&gt;position. The ideal candidate will specialize in family law...&amp;nbsp;&amp;nbsp;...Public Holidays) Family Leave (Maternity, Paternity) Short Term &amp; Long Term &lt;b&gt;Disability &lt;/b&gt; Training &amp; Development Work From Home...</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Warehouse Management System SME</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D75" t="b">
+        <v>1</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>$40 per hour</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="n">
+        <v>40</v>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-5296686882094587526?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=62&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=4&amp;aq=-2800508538475755211&amp;cid=12571&amp;jobAge=54&amp;brelb=100&amp;bscr=66.91787&amp;scr=66.91787</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;job &lt;/b&gt;summary: We are searching for a Warehouse Management System Specialist to travel...&amp;nbsp;&amp;nbsp;...contract to hire position. location: &lt;b&gt;Remote,&lt;/b&gt; Remote job type: Contract salary:...&amp;nbsp;&amp;nbsp;...National Origin, Age, Genetic Information, &lt;b&gt;Disability,&lt;/b&gt; Protected Veteran Status,</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Audit Supervisor</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Gpac</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Randolph, MA</t>
+        </is>
+      </c>
+      <c r="D76" t="b">
+        <v>1</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>$100k - $130k</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="n">
+        <v>100000</v>
+      </c>
+      <c r="M76" t="n">
+        <v>100000</v>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/1384512424790019716?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=63&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=4&amp;aq=-2800508538475755211&amp;cid=12571&amp;jobAge=2478&amp;brelb=100&amp;bscr=66.80147&amp;scr=66.80147</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...Microsoft Word and Excel, ProSystem fx Tax &lt;b&gt;Job &lt;/b&gt;Type : Full-time Pay :$100,000-130,000 Benefits : 401(k), Dental Insurance, &lt;b&gt;Disability &lt;/b&gt;Insurance, Flexible schedule, Health...&amp;nbsp;&amp;nbsp;...Preferred) Work Location : Hybrid / On-Sight / &lt;b&gt;Remote &lt;/b&gt; If you are interested in co</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Physical Therapist - Travel Contract</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Jackson Therapy Partners</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Macomb, MI</t>
+        </is>
+      </c>
+      <c r="D77" t="b">
+        <v>1</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-8722894243988776101?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=64&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=4&amp;aq=-2800508538475755211&amp;cid=12571&amp;jobAge=78&amp;brelb=100&amp;bscr=66.80147&amp;scr=66.80147</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...independently in patient homes. Experience with telehealth or &lt;b&gt;remote &lt;/b&gt;documentation workflows. Assignment Details Shift days:...&amp;nbsp;&amp;nbsp;..., religion, sexual orientation, gender, gender identity and expression, national origin, age, &lt;b&gt;disability,&lt;/b&gt; or protected veteran status..</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Licensed Vocational Nurse (LVN) - Full-Time (HCS Program)</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Adaptive Aids HCS</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Texas</t>
+        </is>
+      </c>
+      <c r="D78" t="b">
+        <v>1</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>$6,000 - $7,500 per month</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="n">
+        <v>72000</v>
+      </c>
+      <c r="M78" t="n">
+        <v>72000</v>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-8913627002404480262?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=65&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=4&amp;aq=-2800508538475755211&amp;cid=12571&amp;jobAge=966&amp;brelb=100&amp;bscr=66.78297&amp;scr=66.78297</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...Combination of on-site visits and limited &lt;b&gt;remote &lt;/b&gt;work (as applicable) Equal Opportunity...&amp;nbsp;&amp;nbsp;...sexual orientation, national origin, age, &lt;b&gt;disability,&lt;/b&gt; veteran status, or any other protected...&amp;nbsp;&amp;nbsp;...individuals with disabilities to perform essential &lt;b&gt;job &lt;/b&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Controls Engineer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Aggreko</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Melbourne, FL</t>
+        </is>
+      </c>
+      <c r="D79" t="b">
+        <v>1</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-5892938641144961837?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=67&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=4&amp;aq=-2800508538475755211&amp;cid=12571&amp;jobAge=6294&amp;brelb=100&amp;bscr=66.77348&amp;scr=66.77348</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...Schneider PLCs, and PlantSCADA/Citect. Knowledge of network design, &lt;b&gt;remote &lt;/b&gt;access, IP networking, VLANs, and routing. Excellent problem...&amp;nbsp;&amp;nbsp;...on your race, colour, ethnicity, religion, sex, sexual orientation, gender identity, national origin, &lt;b&gt;disability,&lt;/b&gt; or veteran</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Credentialing Specialist</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Caravel Autism Health</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Spokane, WA</t>
+        </is>
+      </c>
+      <c r="D80" t="b">
+        <v>1</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>$18 per hour</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="n">
+        <v>18</v>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-4042960260759505990?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=68&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=4&amp;aq=-2800508538475755211&amp;cid=12571&amp;jobAge=246&amp;brelb=100&amp;bscr=66.77348&amp;scr=66.77348</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...medical and dental insurance, employer-matched 401(k), paid time-off, paid travel, short-term &lt;b&gt;disability &lt;/b&gt;and more. Important: Credentialing Specialist is a Full Time &lt;b&gt;remote/&lt;/b&gt;work from home opportunity, and we are open to candidates in the Spokane, WA OR Green Bay, WI...&amp;nbsp;</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Patent Agent</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Cepheid</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Marlborough, MA</t>
+        </is>
+      </c>
+      <c r="D81" t="b">
+        <v>1</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>$134.33k - $148k</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="n">
+        <v>134330</v>
+      </c>
+      <c r="M81" t="n">
+        <v>134330</v>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-2353322042964982869?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=69&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=4&amp;aq=-2800508538475755211&amp;cid=12571&amp;jobAge=147&amp;brelb=100&amp;bscr=66.60055&amp;scr=66.60055</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...IP team. The role is designated as fully &lt;b&gt;remote;&lt;/b&gt; however, there is a strong preference for...&amp;nbsp;&amp;nbsp;.... The essential requirements of the &lt;b&gt;job &lt;/b&gt;include: Bachelor's degree in...&amp;nbsp;&amp;nbsp;...origin, religion, sex, age, marital status, &lt;b&gt;disability,&lt;/b&gt; veteran status, sex</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Associate Disability Attorney</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Heard &amp; Smith</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>San Antonio, TX</t>
+        </is>
+      </c>
+      <c r="D82" t="b">
+        <v>1</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>internship</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>https://jooble.org/jdp/-555636689245965876?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=70&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=4&amp;aq=-2800508538475755211&amp;cid=12571&amp;jobAge=248&amp;brelb=100&amp;bscr=65.88082&amp;scr=65.88082</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...that helps clients get justice in their &lt;b&gt;disability &lt;/b&gt;claims? Heard &amp; Smith’s core values remind...&amp;nbsp;&amp;nbsp;...of the Heard &amp; Smith team is more than a &lt;b&gt;job;&lt;/b&gt; each day provides you with opportunities...&amp;nbsp;&amp;nbsp;...Listed States Minimum Requirements for a &lt;b&gt;Remote &lt;/b&gt;Attorne</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>PMHNP</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Rooted Talent Solutions</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="D83" t="b">
+        <v>1</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-6314962688405278287?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=71&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=4&amp;aq=-2800508538475755211&amp;cid=12571&amp;jobAge=1102&amp;brelb=100&amp;bscr=65.861&amp;scr=65.861</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...&lt;b&gt;Job &lt;/b&gt;Title: Psychiatric Mental Health Nurse Practitioner (PMHNP) – Full-Time (Washington, &lt;b&gt;Remote)&lt;/b&gt; Location: Washington State and New York (Remote) Employment Type: Full-Time...&amp;nbsp;&amp;nbsp;...-paid coverage, including short-term &lt;b&gt;disability &lt;/b&gt; Paid Time Off: 20 PTO days per</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Retail Operations Leader</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Trane Technologies</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="D84" t="b">
+        <v>1</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>$90k</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="n">
+        <v>90000</v>
+      </c>
+      <c r="M84" t="n">
+        <v>90000</v>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-8416517631155995675?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=72&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=4&amp;aq=-2800508538475755211&amp;cid=12571&amp;jobAge=25&amp;brelb=100&amp;bscr=65.861&amp;scr=65.861</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...thrive at work and at home. We boldly go. &lt;b&gt;Job &lt;/b&gt;Summary: The Retail Operations Leader is...&amp;nbsp;&amp;nbsp;...satisfaction. Work Arrangement: &lt;b&gt;Remote &lt;/b&gt;within a Geography (Candidates can live anywhere...&amp;nbsp;&amp;nbsp;...origin, pregnancy, age, marital status, &lt;b&gt;disability,&lt;/b&gt; status as</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Senior Data Governance Consultant</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Data Ideology</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA</t>
+        </is>
+      </c>
+      <c r="D85" t="b">
+        <v>1</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-6316900384086561621?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=73&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=4&amp;aq=-2800508538475755211&amp;cid=12571&amp;jobAge=774&amp;brelb=100&amp;bscr=65.861&amp;scr=65.861</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...Reasonable accommodations may be made to enable individuals with &lt;b&gt;disabilities &lt;/b&gt;to perform essential functions. Other duties may be assigned...&amp;nbsp;&amp;nbsp;...’s preferred but not required) Work Environment: &lt;b&gt;Remote &lt;/b&gt;work from home. Hours of work and days are generally Monday...&amp;nb</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Tax Manager (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Gpac</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>San Antonio, TX</t>
+        </is>
+      </c>
+      <c r="D86" t="b">
+        <v>1</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>$120k - $150k</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="n">
+        <v>120000</v>
+      </c>
+      <c r="M86" t="n">
+        <v>120000</v>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-4858704998413869903?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=74&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=4&amp;aq=-2800508538475755211&amp;cid=12571&amp;jobAge=2742&amp;brelb=100&amp;bscr=65.70347&amp;scr=65.70347</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...CPA firm in the San Antonio, TX area is looking to add a Hybrid/&lt;b&gt;Remote &lt;/b&gt;Tax Manager to their team. This stable and growing firm offers...&amp;nbsp;&amp;nbsp;..., color, sex (including pregnancy), religion, national origin, &lt;b&gt;disability,&lt;/b&gt; sexual orientation, gender identity, marital status</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Remote Recruiter</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Gpac</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Mankato, MN</t>
+        </is>
+      </c>
+      <c r="D87" t="b">
+        <v>1</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>$36k - $150k</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="n">
+        <v>36000</v>
+      </c>
+      <c r="M87" t="n">
+        <v>36000</v>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-3984249272837150827?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=75&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=4&amp;aq=-2800508538475755211&amp;cid=12571&amp;jobAge=2454&amp;brelb=100&amp;bscr=65.70347&amp;scr=65.70347</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...applicants will receive consideration without regard to race, age, color, sex (including pregnancy), religion, national origin, &lt;b&gt;disability,&lt;/b&gt; sexual orientation, gender identity, marital status, military status, genetic information, or any other status protected by applicable...&amp;nbsp;</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Remote Sales Executive/Freight Broker</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Gpac</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Memphis, TN</t>
+        </is>
+      </c>
+      <c r="D88" t="b">
+        <v>1</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>$80k - $125k</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="n">
+        <v>80000</v>
+      </c>
+      <c r="M88" t="n">
+        <v>80000</v>
+      </c>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-4413348339129082430?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=76&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=4&amp;aq=-2800508538475755211&amp;cid=12571&amp;jobAge=2958&amp;brelb=100&amp;bscr=65.70347&amp;scr=65.70347</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...applicants will receive consideration without regard to race, age, color, sex (including pregnancy), religion, national origin, &lt;b&gt;disability,&lt;/b&gt; sexual orientation, gender identity, marital status, military status, genetic information, or any other status protected by applicable...&amp;nbsp;</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Truss Design Manager</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Gpac</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Westminster, CO</t>
+        </is>
+      </c>
+      <c r="D89" t="b">
+        <v>1</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>$72k - $95k</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="n">
+        <v>72000</v>
+      </c>
+      <c r="M89" t="n">
+        <v>72000</v>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/4119903343183792505?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=77&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=4&amp;aq=-2800508538475755211&amp;cid=12571&amp;jobAge=3078&amp;brelb=100&amp;bscr=65.70347&amp;scr=65.70347</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>Truss Design Manager &lt;b&gt;Job &lt;/b&gt;Description We are looking for an individual that has proven...&amp;nbsp;&amp;nbsp;...keep projects progressing on time with &lt;b&gt;remote &lt;/b&gt;Designers. Requirements: * Miket...&amp;nbsp;&amp;nbsp;...including pregnancy), religion, national origin, &lt;b&gt;disability,&lt;/b&gt; sexual orientation,</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Remote Transportation Sales Executive</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Gpac</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Manhattan, KS</t>
+        </is>
+      </c>
+      <c r="D90" t="b">
+        <v>1</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>$70k - $90k</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="n">
+        <v>70000</v>
+      </c>
+      <c r="M90" t="n">
+        <v>70000</v>
+      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/4608178633459144191?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=78&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=4&amp;aq=-2800508538475755211&amp;cid=12571&amp;jobAge=2454&amp;brelb=100&amp;bscr=65.70347&amp;scr=65.70347</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...applicants will receive consideration without regard to race, age, color, sex (including pregnancy), religion, national origin, &lt;b&gt;disability,&lt;/b&gt; sexual orientation, gender identity, marital status, military status, genetic information, or any other status protected by applicable...&amp;nbsp;</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Abestos Trust Bankruptcy Attorney</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Gpac</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Washington DC</t>
+        </is>
+      </c>
+      <c r="D91" t="b">
+        <v>1</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>$100k - $250k</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="n">
+        <v>100000</v>
+      </c>
+      <c r="M91" t="n">
+        <v>100000</v>
+      </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-3309207506167211724?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=79&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=4&amp;aq=-2800508538475755211&amp;cid=12571&amp;jobAge=2574&amp;brelb=100&amp;bscr=65.70347&amp;scr=65.70347</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>A growing firm is seeking a &lt;b&gt;REMOTE &lt;/b&gt;Abestos Trust Bankruptcy Attorney. We are seeking an Attorney with Abestos litigation and Bankruptcy...&amp;nbsp;&amp;nbsp;..., color, sex (including pregnancy), religion, national origin, &lt;b&gt;disability,&lt;/b&gt; sexual orientation, gender identity, marital status, milit</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Construction Defect Attorney</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Gpac</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>San Diego, CA</t>
+        </is>
+      </c>
+      <c r="D92" t="b">
+        <v>1</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>$150k - $250k</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="n">
+        <v>150000</v>
+      </c>
+      <c r="M92" t="n">
+        <v>150000</v>
+      </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-2657795492798445481?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=80&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=4&amp;aq=-2800508538475755211&amp;cid=12571&amp;jobAge=3006&amp;brelb=100&amp;bscr=65.61047&amp;scr=65.61047</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>Construction Defect Attorney (1-15 Years Experience) Location: Fully &lt;b&gt;Remote &lt;/b&gt;(Anywhere in California or Outside CA) CA Bar Admission...&amp;nbsp;&amp;nbsp;..., color, sex (including pregnancy), religion, national origin, &lt;b&gt;disability,&lt;/b&gt; sexual orientation, gender identity, marital status, military.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Hybrid/Remote Tax Senior Associate</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Gpac</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="D93" t="b">
+        <v>1</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>$80k - $105k</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="n">
+        <v>80000</v>
+      </c>
+      <c r="M93" t="n">
+        <v>80000</v>
+      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-2534014813088552576?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=81&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=5&amp;aq=7729912916964402983&amp;cid=12571&amp;jobAge=2406&amp;brelb=100&amp;bscr=65.61047&amp;scr=65.61047</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...Compensation: * $80,000-$100,000 * Excellent benefits package * Hyrbid/&lt;b&gt;Remote &lt;/b&gt;role To be considered, please apply with a resume. If you...&amp;nbsp;&amp;nbsp;..., color, sex (including pregnancy), religion, national origin, &lt;b&gt;disability,&lt;/b&gt; sexual orientation, gender identity, marital stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Remote - Tax Senior</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Gpac</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>San Diego, CA</t>
+        </is>
+      </c>
+      <c r="D94" t="b">
+        <v>1</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>$80k - $120k</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="n">
+        <v>80000</v>
+      </c>
+      <c r="M94" t="n">
+        <v>80000</v>
+      </c>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-8422294831123100360?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=82&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=5&amp;aq=7729912916964402983&amp;cid=12571&amp;jobAge=3078&amp;brelb=100&amp;bscr=65.61047&amp;scr=65.61047</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...applicants will receive consideration without regard to race, age, color, sex (including pregnancy), religion, national origin, &lt;b&gt;disability,&lt;/b&gt; sexual orientation, gender identity, marital status, military status, genetic information, or any other status protected by applicable...&amp;nbsp;</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Tax Senior - Remote</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Gpac</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D95" t="b">
+        <v>1</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>$80k - $110k</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="n">
+        <v>80000</v>
+      </c>
+      <c r="M95" t="n">
+        <v>80000</v>
+      </c>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/3546963547734474358?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=83&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=5&amp;aq=7729912916964402983&amp;cid=12571&amp;jobAge=3078&amp;brelb=100&amp;bscr=65.61047&amp;scr=65.61047</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...applicants will receive consideration without regard to race, age, color, sex (including pregnancy), religion, national origin, &lt;b&gt;disability,&lt;/b&gt; sexual orientation, gender identity, marital status, military status, genetic information, or any other status protected by applicable...&amp;nbsp;</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Hybrid/Remote Tax Senior</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Gpac</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Dallas, TX</t>
+        </is>
+      </c>
+      <c r="D96" t="b">
+        <v>1</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>$85k - $105k</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="n">
+        <v>85000</v>
+      </c>
+      <c r="M96" t="n">
+        <v>85000</v>
+      </c>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-2196199468883350162?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=84&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=5&amp;aq=7729912916964402983&amp;cid=12571&amp;jobAge=2742&amp;brelb=100&amp;bscr=65.56059&amp;scr=65.56059</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...applicants will receive consideration without regard to race, age, color, sex (including pregnancy), religion, national origin, &lt;b&gt;disability,&lt;/b&gt; sexual orientation, gender identity, marital status, military status, genetic information, or any other status protected by applicable...&amp;nbsp;</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Tax Manager</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Gpac</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Houston, TX</t>
+        </is>
+      </c>
+      <c r="D97" t="b">
+        <v>1</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>$130k - $180k</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="n">
+        <v>130000</v>
+      </c>
+      <c r="M97" t="n">
+        <v>130000</v>
+      </c>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/3680306443348206180?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=85&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=5&amp;aq=7729912916964402983&amp;cid=12571&amp;jobAge=2406&amp;brelb=100&amp;bscr=65.56059&amp;scr=65.56059</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...30,000-180,000 * Excellent benefits package+Bonuses * Hybrid/&lt;b&gt;Remote &lt;/b&gt;role To be considered, please apply with a resume. If you have...&amp;nbsp;&amp;nbsp;..., color, sex (including pregnancy), religion, national origin, &lt;b&gt;disability,&lt;/b&gt; sexual orientation, gender identity, marital status, m</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Non-Surgical IME Opening for Orthopedic Surgery Expert in NY | Earn 1 Million</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Confidential</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Brooklyn, NY</t>
+        </is>
+      </c>
+      <c r="D98" t="b">
+        <v>1</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/6925386835275945871?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=86&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=5&amp;aq=7729912916964402983&amp;cid=12571&amp;jobAge=6&amp;brelb=100&amp;bscr=65.434906&amp;scr=65.434906</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...flexible- Design your own schedule * Determine level of patient &lt;b&gt;disability &lt;/b&gt;for insurance companies, mostly worker's compensation cases...&amp;nbsp;&amp;nbsp;...County, Rockland County, Orange County, Westchester County * No &lt;b&gt;remote &lt;/b&gt;option For more information, please contact: Christen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Audit Manager</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Gpac</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Tucson, AZ</t>
+        </is>
+      </c>
+      <c r="D99" t="b">
+        <v>1</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>$105k - $145k</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="n">
+        <v>105000</v>
+      </c>
+      <c r="M99" t="n">
+        <v>105000</v>
+      </c>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/6131967727623025471?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=87&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=5&amp;aq=7729912916964402983&amp;cid=12571&amp;jobAge=2526&amp;brelb=100&amp;bscr=65.19336&amp;scr=65.19336</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...reviews and compilations in the office or &lt;b&gt;remotely!&lt;/b&gt; Audit Manager Functions: Manage financial...&amp;nbsp;&amp;nbsp;...-$145,000 * Excellent Benefits Package &lt;b&gt;Job &lt;/b&gt;Type : Full-time Pay : $105,000-$145,000 Benefits: 401(k), Dental Insurance, &lt;b&gt;Disability &lt;/b&gt;Insurance, Flexible schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Sales Associate (Remote)</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Spieldenner Financial Group</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Colorado Springs, CO</t>
+        </is>
+      </c>
+      <c r="D100" t="b">
+        <v>1</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>$500 - $2,000 per month</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="n">
+        <v>6000</v>
+      </c>
+      <c r="M100" t="n">
+        <v>6000</v>
+      </c>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/5462195536804532890?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=88&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=5&amp;aq=7729912916964402983&amp;cid=12571&amp;jobAge=462&amp;brelb=100&amp;bscr=65.19336&amp;scr=65.19336</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...allows our agents to have a competitive edge in the industry. &lt;b&gt;Job &lt;/b&gt;Duties: Setting Appointments: 6-8 hours per week: reaching...&amp;nbsp;&amp;nbsp;...options to meet their financial need in the case of a death or &lt;b&gt;disability.&lt;/b&gt; Meeting with Families: 2 days per week: meeting with...&amp;nbsp</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Sales Agent - Remote</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>True North Recruiters</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>San Antonio, TX</t>
+        </is>
+      </c>
+      <c r="D101" t="b">
+        <v>1</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>$50k - $150k</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="n">
+        <v>50000</v>
+      </c>
+      <c r="M101" t="n">
+        <v>50000</v>
+      </c>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/7763528873586976212?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=89&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=5&amp;aq=7729912916964402983&amp;cid=12571&amp;jobAge=438&amp;brelb=100&amp;bscr=65.19336&amp;scr=65.19336</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...&lt;b&gt;Job &lt;/b&gt;Description IF YOU ARE ALREADY LIFE &amp; HEALTH LICENSED YOU CAN GET STARTED...&amp;nbsp;&amp;nbsp;...their needs for mortgage, life, &lt;b&gt;disability &lt;/b&gt;and other income protection needs...&amp;nbsp;&amp;nbsp;...looking YES! YOU CAN WORK FROM HOME OR &lt;b&gt;REMOTE &lt;/b&gt;VIA PHONE OR ZOOM Requirements...&amp;n</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Hybrid Board Certified Behavior Analyst (BCBA) - Remote In-Person</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Centria Autism</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Bowie, TX</t>
+        </is>
+      </c>
+      <c r="D102" t="b">
+        <v>1</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>$90k - $105k</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="n">
+        <v>90000</v>
+      </c>
+      <c r="M102" t="n">
+        <v>90000</v>
+      </c>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-7866772035980272777?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=90&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=5&amp;aq=7729912916964402983&amp;cid=12571&amp;jobAge=198&amp;brelb=100&amp;bscr=65.17885&amp;scr=65.17885</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...Flexibility with Clinical Connection Split your time between &lt;b&gt;remote &lt;/b&gt;supervision planning and collaboration and in-person visits that...&amp;nbsp;&amp;nbsp;...religion sex sexual orientation gender identity national origin &lt;b&gt;disability &lt;/b&gt;or protected veteran status. Required Experience: IC</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Junior Associate Disability Attorney</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Heard &amp; Smith</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>San Antonio, TX</t>
+        </is>
+      </c>
+      <c r="D103" t="b">
+        <v>1</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>internship</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>$50k - $65k</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K103" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>https://jooble.org/jdp/-7371745694932741232?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=91&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=5&amp;aq=7729912916964402983&amp;cid=12571&amp;jobAge=248&amp;brelb=100&amp;bscr=65.17885&amp;scr=65.17885</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...that helps clients get justice in their &lt;b&gt;disability &lt;/b&gt;claims? Heard &amp; Smith’s core values remind...&amp;nbsp;&amp;nbsp;...of the Heard &amp; Smith team is more than a &lt;b&gt;job;&lt;/b&gt; each day provides you with opportunities...&amp;nbsp;&amp;nbsp;...Not Required Minimum Requirements for a &lt;b&gt;Remote &lt;/b&gt;Attorney</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Remote Consumable Sales-Shandong</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Agilent Technologies</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="D104" t="b">
+        <v>1</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-1927593046359427040?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=92&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=5&amp;aq=7729912916964402983&amp;cid=12571&amp;jobAge=54&amp;brelb=100&amp;bscr=65.16406&amp;scr=65.16406</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...&lt;b&gt;Job &lt;/b&gt;Description • 销售仪器耗材和消耗品，如色谱柱、样品制备和耗材等核心产品，覆盖指定区域。 • 积极响应客户需求，执行销售计划，推动业务增长。 • 有效开拓目标业务的新客户，深入渗透关键客户群体，识别潜在商机。 • 制定明确的销售目标...&amp;nbsp;&amp;nbsp;...orientation, gender identity, national origin, protected veteran status, &lt;b&gt;disability &lt;/b&gt;or any other protected categories under all appli</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Remote Administrative Assistant - National Accounts</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Carter Lumber</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Kent, OH</t>
+        </is>
+      </c>
+      <c r="D105" t="b">
+        <v>1</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/4427906293720554037?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=93&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=5&amp;aq=7729912916964402983&amp;cid=12571&amp;jobAge=54&amp;brelb=100&amp;bscr=65.10452&amp;scr=65.10452</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...This is a &lt;b&gt;remote/&lt;/b&gt;virtual position. You can work from home! Carter Lumber has an amazing opportunity to be a remote Administrative...&amp;nbsp;&amp;nbsp;...) available after 30 days of employment Short and Long-Term &lt;b&gt;Disability &lt;/b&gt; Company-paid life insurance and AD&amp;D Optional supplemental</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Primary Care Physician - Boston | Capped Panel &amp; Team Support</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Confidential</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Boston, MA</t>
+        </is>
+      </c>
+      <c r="D106" t="b">
+        <v>1</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-3584417692626141326?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=94&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=5&amp;aq=7729912916964402983&amp;cid=12571&amp;jobAge=54&amp;brelb=100&amp;bscr=65.100555&amp;scr=65.100555</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...Schedule flexibility built in Administrative days can be completed &lt;b&gt;remotely.&lt;/b&gt; We're designed to support sustainable, long-term practice -...&amp;nbsp;&amp;nbsp;...sexual orientation), national origin, marital status, age, &lt;b&gt;disability,&lt;/b&gt; political beliefs, military experience, genetic info</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Clinical Social Worker / Part-time (REMOTE)</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Acentra Health, LLC</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Maine</t>
+        </is>
+      </c>
+      <c r="D107" t="b">
+        <v>1</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>$32.35 - $38.46 per hour</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="n">
+        <v>32</v>
+      </c>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-6743116081726947280?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=95&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=5&amp;aq=7729912916964402983&amp;cid=12571&amp;jobAge=822&amp;brelb=100&amp;bscr=65.100555&amp;scr=65.100555</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...being a vital partner for health solutions in the public sector. &lt;b&gt;Job &lt;/b&gt;Summary and Responsibilities: Acentra Health is looking for a...&amp;nbsp;&amp;nbsp;...of interest. Best of luck in your search! EEO AA M/F/Vet/&lt;b&gt;Disability &lt;/b&gt; Acentra Health is an Equal Opportunity Employer. All...&amp;nbsp</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Tax Senior</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Gpac</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Arlington, TX</t>
+        </is>
+      </c>
+      <c r="D108" t="b">
+        <v>1</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>$75k - $110k</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="n">
+        <v>75000</v>
+      </c>
+      <c r="M108" t="n">
+        <v>75000</v>
+      </c>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/2892410725523912029?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=97&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=5&amp;aq=7729912916964402983&amp;cid=12571&amp;jobAge=3078&amp;brelb=100&amp;bscr=65.06571&amp;scr=65.06571</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...CPA firm in the Arlington, TX area is looking to add a Hybrid/&lt;b&gt;Remote &lt;/b&gt;Tax Senior to their team. This stable and growing firm offers their...&amp;nbsp;&amp;nbsp;..., color, sex (including pregnancy), religion, national origin, &lt;b&gt;disability,&lt;/b&gt; sexual orientation, gender identity, marital sta</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Area Sales Manager Bilingual Spanish</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Mahoney Environmental Solutions</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Miami, FL</t>
+        </is>
+      </c>
+      <c r="D109" t="b">
+        <v>1</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>$60k - $62.5k</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="n">
+        <v>60000</v>
+      </c>
+      <c r="M109" t="n">
+        <v>60000</v>
+      </c>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/2994726898741844849?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=98&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=5&amp;aq=7729912916964402983&amp;cid=12571&amp;jobAge=246&amp;brelb=100&amp;bscr=65.05834&amp;scr=65.05834</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...to you! This is not your typical sales &lt;b&gt;job &lt;/b&gt;and we are NOT looking for your typical sales...&amp;nbsp;&amp;nbsp;...first year. • Office from home / Work &lt;b&gt;remote.&lt;/b&gt; • Car allowance. • Company provided...&amp;nbsp;&amp;nbsp;..., sex, national origin, religion, age, &lt;b&gt;disability,&lt;/b&gt; genetic inform</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Real Estate Attorney</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Gpac</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
+      <c r="D110" t="b">
+        <v>1</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>$200k - $275k</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="n">
+        <v>200000</v>
+      </c>
+      <c r="M110" t="n">
+        <v>200000</v>
+      </c>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/2835153043718989234?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=99&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=5&amp;aq=7729912916964402983&amp;cid=12571&amp;jobAge=2766&amp;brelb=100&amp;bscr=64.92389&amp;scr=64.92389</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>Real Estate Attorney - Transactions &amp; Development (Los Angeles | &lt;b&gt;Remote &lt;/b&gt;in CA) A well-established firm focused on real estate law is...&amp;nbsp;&amp;nbsp;..., color, sex (including pregnancy), religion, national origin, &lt;b&gt;disability,&lt;/b&gt; sexual orientation, gender identity, marital status, military</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Revenue Cycle Billing Specialists - Mogel</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Qureos Inc</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Gilbert, AZ</t>
+        </is>
+      </c>
+      <c r="D111" t="b">
+        <v>1</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>keyword_pwd</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>$24 - $27 per hour</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="n">
+        <v>24</v>
+      </c>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>https://jooble.org/desc/-8990523424944491195?ckey=divyang+PwBD+disability+jobs+remote&amp;rgn=55126&amp;pos=100&amp;groupId=-1621594173&amp;elckey=-4613538556171688043&amp;p=5&amp;aq=7729912916964402983&amp;cid=12571&amp;jobAge=194&amp;brelb=100&amp;bscr=65.09278&amp;scr=65.09278</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>google_jobs</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>&amp;nbsp;...Onsite: Monday–Wednesday &amp; Friday &lt;b&gt;Remote:&lt;/b&gt; Thursdays Schedule remains consistent...&amp;nbsp;&amp;nbsp;...applicants. Hiring decisions are based on &lt;b&gt;job-&lt;/b&gt;related qualifications without regard to...&amp;nbsp;&amp;nbsp;...sexual orientation, national origin, age, &lt;b&gt;disability,&lt;/b&gt; veteran status,</t>
         </is>
       </c>
     </row>
